--- a/src/pages/event/交流会.xlsx
+++ b/src/pages/event/交流会.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\himur\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\himur\Documents\Develop\sales\src\pages\event\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A040D1-793E-4A6E-8FBB-4A9A285B91CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0F4A2D-B1D6-477D-9DF2-AF5BD6A4F801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21975" yWindow="-16035" windowWidth="26610" windowHeight="15075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5355" yWindow="-15285" windowWidth="25800" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2025'!$A$2:$K$368</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2025'!$A$2:$K$578</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2025'!$A$2:$K$641</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3532" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4055" uniqueCount="1041">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -3626,6 +3626,415 @@
   <si>
     <t>SORART</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">㈱NEXTTECHNOLOGY  </t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/1832cc2f128b7767c6cf9a97e03e7840/</t>
+  </si>
+  <si>
+    <t>株式会社ゼネット</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/d9919440c804d7576050a2f3da7b589c/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">株式会社NEXTTECHNOLOGY  </t>
+    <rPh sb="0" eb="4">
+      <t>カブシキガイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市ヶ谷</t>
+    <rPh sb="0" eb="3">
+      <t>イチガヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インフラ・SES交流会</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/sora260929/</t>
+  </si>
+  <si>
+    <t>生成AIビジネス交流会</t>
+  </si>
+  <si>
+    <t>株式会社Koinobori</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/c2ee8ea9ee8d411aa750a27e76eccfcd/</t>
+  </si>
+  <si>
+    <t>溜池山王</t>
+    <rPh sb="0" eb="4">
+      <t>タメイケサンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/d9acf2177a450e09c8d88f4a40297d64/</t>
+  </si>
+  <si>
+    <t>株式会社アイデンティティー</t>
+    <rPh sb="0" eb="4">
+      <t>カブシキガイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/35c2a681f63fce4034c3160866d9f475/3884262/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受託開発売上UP戦略トークセッション&amp;交流会 </t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/752af8969f0ffad03f9bb28881ae29b7/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/a12dc96bd202c065fcb44cfdf2abd5e0/</t>
+  </si>
+  <si>
+    <t>株式会社クラウドナイン</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/7c6f9023d14dbad9fe86fd2c92d11cab/</t>
+  </si>
+  <si>
+    <t>SESセミナー＆交流会</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/58de0a5f06043b4dc4f49f4b85a62a76/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/ses_tsudoiB/</t>
+  </si>
+  <si>
+    <t>https://www.z2024.jp/event-details/shinjuku-ses-meetup-202610</t>
+  </si>
+  <si>
+    <t>乃木坂</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/875b8cbefacc2a4fd73ccfd3690c32b6/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/1c340f8dc8670a2caffde96f7dd9061d/</t>
+  </si>
+  <si>
+    <t>株式会社ポジポジ</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/fc4a9c110e7099495207269049841052/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/c3856912042c531fbe3718fa848cc86f/3898731/</t>
+  </si>
+  <si>
+    <t>https://www.z2024.jp/event-details/toyochyou-futsal-meetup202610</t>
+  </si>
+  <si>
+    <t>ROSCA株式会社</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/4e43b9d4c97cad5efecda09398f069cc/</t>
+  </si>
+  <si>
+    <t>渋谷SES/ITビジネス交流会</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/4cfea4702383a1db71e91cbcc10abdf3/3881155/</t>
+  </si>
+  <si>
+    <t>QA・ソフトウェアテスト交流会</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/sora_test26/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/8ca32436774dfe72ff794805b0ff48e2/</t>
+  </si>
+  <si>
+    <t>銀座</t>
+    <rPh sb="0" eb="2">
+      <t>ギンザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/revision_261008/</t>
+  </si>
+  <si>
+    <t>SES交流会/勉強会</t>
+    <rPh sb="3" eb="6">
+      <t>コウリュウカイ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ベンキョウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>株式会社テックピット </t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/1b80b9efe85a7fd66e25b8fc9cc2ff3f/</t>
+  </si>
+  <si>
+    <t>13:45〜15:00</t>
+  </si>
+  <si>
+    <t>AppTime</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/c6905b69af9823c87463190217ee1cdf/</t>
+  </si>
+  <si>
+    <t>第1回SPC/SES情報交換会</t>
+  </si>
+  <si>
+    <t>株式会社イノベイティア</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/s/date-20261009/?q=SES%E4%BA%A4%E6%B5%81%E4%BC%9A</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/cd5c44145116de48b3432c2a922c7e30/</t>
+  </si>
+  <si>
+    <t>SESビジネス交流会</t>
+    <rPh sb="7" eb="10">
+      <t>コウリュウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビート・イット</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/1f9d3d8bf19de6c74358d7d3b0ff59b1/</t>
+  </si>
+  <si>
+    <t>10:15〜12:00</t>
+  </si>
+  <si>
+    <t>株式会社テンプラス</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/282dc594312e40e4364b227841e1c5c2/3881009/</t>
+  </si>
+  <si>
+    <t>WEB、IT、デザイナー、クリエイターさん限定ビジネスマッチング交流会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/bae1144afddae369142a20e207c0088d/</t>
+  </si>
+  <si>
+    <t>三田</t>
+    <rPh sb="0" eb="2">
+      <t>ミタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SES・IT情報交流会</t>
+  </si>
+  <si>
+    <t>Re Force株式会社</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/8a4ba332e7172f4a54a793e776dc2908/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/02297807a3842b054ff874bbfa0d18af/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/5ab464be1d07f3dacb1a4650589b5e23/3898733/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/418fa971ed66e794ce1ac3956dfcf5b4/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/751a259d2d84487aae21976c35f65abe/3893742/</t>
+  </si>
+  <si>
+    <t>SkillDB交流会</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/4963c2ff2ddf3b1fd4a426315db46618/</t>
+  </si>
+  <si>
+    <t>株式会社PURGATORIA／Spurs株式会社</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20:00〜21:00</t>
+  </si>
+  <si>
+    <t>東京IT交流会</t>
+    <rPh sb="0" eb="2">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>コウリュウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/1d232591a471344cf0d5c4825511b348/</t>
+  </si>
+  <si>
+    <t>https://www.z2024.jp/event-details/akihabara-ses-202610</t>
+  </si>
+  <si>
+    <t>https://sepex.jp/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/0eda976ce6f77998cfe4f56fd4c835db/3898895/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/c3856912042c531fbe3718fa848cc86f/3899107/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/revision_261021/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/2a080f8cdcb36c1ce814076154adcd0e/</t>
+  </si>
+  <si>
+    <t>こむこむ交流会</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/b03506026e994f20c22375bca5cc100a/</t>
+  </si>
+  <si>
+    <t>株式会社アクア  </t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/92bd81c7bc4a8047c551f5bdc6102eef/</t>
+  </si>
+  <si>
+    <t>交流会</t>
+    <rPh sb="0" eb="3">
+      <t>コウリュウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/a3dddeba1cbcf07676be769643fb5186/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/511529fb326b50295e89d9aaedc2fee3/</t>
+  </si>
+  <si>
+    <t>SES/ITビジネス交流会</t>
+    <rPh sb="10" eb="13">
+      <t>コウリュウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/9b09f656c2f43ace22945ddc75dadffc/3881177/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/sorart0729/3881690/</t>
+  </si>
+  <si>
+    <t>Qoala</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/qoala_ses_261023/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/45420573e79a6eb0c790a3b7de4a9fc5/</t>
+  </si>
+  <si>
+    <t>SES営業・BP開拓担当者交流会</t>
+    <rPh sb="3" eb="5">
+      <t>エイギョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイタク</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>コウリュウカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/5ca88ce194fea2f13cd7f4f59b262fb8/3894681/</t>
+  </si>
+  <si>
+    <t>https://www.z2024.jp/event-details/omiya-ses-it-meetup2610</t>
+  </si>
+  <si>
+    <t>Web・アプリ・業務システム開発ビジネス交流会</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/20261027sora/</t>
+  </si>
+  <si>
+    <t>株式会社アジアンビジネスネットワーク／株式会社ラプテック　</t>
+    <rPh sb="0" eb="4">
+      <t>カブシキガイシャ</t>
+    </rPh>
+    <rPh sb="19" eb="23">
+      <t>カブシキガイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.z2024.jp/event-details/shinjuku-ses-meetup-202611</t>
+  </si>
+  <si>
+    <t>株式会社LEGAREA</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/070648a163e63405efd5618c03b58d5e/</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/5f1913fbfdd92ed6428af74892bfff1b/</t>
+  </si>
+  <si>
+    <t>https://www.z2024.jp/event-details/toyochyou-futsal-meetup202611</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/12b10f5c46f08350002f8caef61f1a5b/</t>
+  </si>
+  <si>
+    <t>https://www.z2024.jp/event-details/yokohama-meetup2611</t>
+  </si>
+  <si>
+    <t>https://www.z2024.jp/event-details/sapporo-ses-202611</t>
+  </si>
+  <si>
+    <t>少し早めのIT企業忘年会</t>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/2a05f207a012bd54833d1ed3d814d129/</t>
+  </si>
+  <si>
+    <t>株式会社セラク</t>
+    <rPh sb="0" eb="4">
+      <t>カブシキガイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.kokuchpro.com/event/4f73e9ba3038672831abc1dc144d4bbe/</t>
+  </si>
+  <si>
+    <t>https://www.z2024.jp/event-details/akihabara-ses-202611</t>
+  </si>
+  <si>
+    <t>https://www.z2024.jp/event-details/nagoya-ses-it-meetup2611</t>
   </si>
 </sst>
 </file>
@@ -4117,12 +4526,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4132,13 +4535,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4155,6 +4552,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4445,7 +4854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L587"/>
+  <dimension ref="A1:L650"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="16" bestFit="1" customWidth="1"/>
@@ -4496,10 +4905,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.45" thickBot="1">
-      <c r="A2" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="67"/>
+      <c r="A2" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="76"/>
       <c r="C2" s="23" t="s">
         <v>1</v>
       </c>
@@ -20093,7 +20502,7 @@
       <c r="I456" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J456" s="74" t="s">
+      <c r="J456" s="70" t="s">
         <v>849</v>
       </c>
       <c r="K456" s="1" t="s">
@@ -20129,7 +20538,7 @@
       <c r="I457" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J457" s="74" t="s">
+      <c r="J457" s="70" t="s">
         <v>850</v>
       </c>
       <c r="K457" s="1" t="s">
@@ -20165,7 +20574,7 @@
       <c r="I458" s="38" t="s">
         <v>852</v>
       </c>
-      <c r="J458" s="75" t="s">
+      <c r="J458" s="71" t="s">
         <v>853</v>
       </c>
       <c r="K458" s="1" t="s">
@@ -20201,7 +20610,7 @@
       <c r="I459" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J459" s="74" t="s">
+      <c r="J459" s="70" t="s">
         <v>854</v>
       </c>
       <c r="K459" s="1" t="s">
@@ -20237,7 +20646,7 @@
       <c r="I460" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J460" s="74" t="s">
+      <c r="J460" s="70" t="s">
         <v>856</v>
       </c>
       <c r="K460" s="1" t="s">
@@ -20273,7 +20682,7 @@
       <c r="I461" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="J461" s="76" t="s">
+      <c r="J461" s="72" t="s">
         <v>858</v>
       </c>
       <c r="K461" s="1" t="s">
@@ -20285,7 +20694,7 @@
         <v>46269</v>
       </c>
       <c r="B462" s="27" t="str">
-        <f t="shared" ref="B462:B499" si="44">TEXT(A462,"aaa")</f>
+        <f t="shared" ref="B462:B507" si="44">TEXT(A462,"aaa")</f>
         <v>金</v>
       </c>
       <c r="C462" s="28" t="s">
@@ -20309,7 +20718,7 @@
       <c r="I462" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J462" s="74" t="s">
+      <c r="J462" s="70" t="s">
         <v>860</v>
       </c>
       <c r="K462" s="1" t="s">
@@ -20345,7 +20754,7 @@
       <c r="I463" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J463" s="74" t="s">
+      <c r="J463" s="70" t="s">
         <v>864</v>
       </c>
       <c r="K463" s="1" t="s">
@@ -20381,7 +20790,7 @@
       <c r="I464" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="J464" s="74" t="s">
+      <c r="J464" s="70" t="s">
         <v>867</v>
       </c>
       <c r="K464" s="1" t="s">
@@ -20417,7 +20826,7 @@
       <c r="I465" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J465" s="74" t="s">
+      <c r="J465" s="70" t="s">
         <v>868</v>
       </c>
       <c r="K465" s="1" t="s">
@@ -20453,7 +20862,7 @@
       <c r="I466" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J466" s="74" t="s">
+      <c r="J466" s="70" t="s">
         <v>869</v>
       </c>
       <c r="K466" s="1" t="s">
@@ -20489,7 +20898,7 @@
       <c r="I467" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J467" s="74" t="s">
+      <c r="J467" s="70" t="s">
         <v>870</v>
       </c>
       <c r="K467" s="1" t="s">
@@ -20525,7 +20934,7 @@
       <c r="I468" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J468" s="74" t="s">
+      <c r="J468" s="70" t="s">
         <v>873</v>
       </c>
       <c r="K468" s="1" t="s">
@@ -20561,7 +20970,7 @@
       <c r="I469" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J469" s="74" t="s">
+      <c r="J469" s="70" t="s">
         <v>874</v>
       </c>
       <c r="K469" s="1" t="s">
@@ -20597,7 +21006,7 @@
       <c r="I470" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J470" s="74" t="s">
+      <c r="J470" s="70" t="s">
         <v>876</v>
       </c>
       <c r="K470" s="1" t="s">
@@ -20633,7 +21042,7 @@
       <c r="I471" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J471" s="74" t="s">
+      <c r="J471" s="70" t="s">
         <v>878</v>
       </c>
       <c r="K471" s="1" t="s">
@@ -20669,7 +21078,7 @@
       <c r="I472" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J472" s="74" t="s">
+      <c r="J472" s="70" t="s">
         <v>36</v>
       </c>
       <c r="K472" s="1" t="s">
@@ -20705,7 +21114,7 @@
       <c r="I473" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J473" s="74" t="s">
+      <c r="J473" s="70" t="s">
         <v>879</v>
       </c>
       <c r="K473" s="1" t="s">
@@ -20741,7 +21150,7 @@
       <c r="I474" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J474" s="77" t="s">
+      <c r="J474" s="73" t="s">
         <v>36</v>
       </c>
       <c r="K474" s="1" t="s">
@@ -20777,7 +21186,7 @@
       <c r="I475" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J475" s="74" t="s">
+      <c r="J475" s="70" t="s">
         <v>882</v>
       </c>
       <c r="K475" s="1" t="s">
@@ -20813,7 +21222,7 @@
       <c r="I476" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J476" s="77" t="s">
+      <c r="J476" s="73" t="s">
         <v>36</v>
       </c>
       <c r="K476" s="1" t="s">
@@ -20849,7 +21258,7 @@
       <c r="I477" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J477" s="74" t="s">
+      <c r="J477" s="70" t="s">
         <v>885</v>
       </c>
       <c r="K477" s="1" t="s">
@@ -20885,7 +21294,7 @@
       <c r="I478" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J478" s="74" t="s">
+      <c r="J478" s="70" t="s">
         <v>887</v>
       </c>
       <c r="K478" s="1" t="s">
@@ -20921,7 +21330,7 @@
       <c r="I479" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J479" s="74" t="s">
+      <c r="J479" s="70" t="s">
         <v>891</v>
       </c>
       <c r="K479" s="1" t="s">
@@ -20957,7 +21366,7 @@
       <c r="I480" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="J480" s="74" t="s">
+      <c r="J480" s="70" t="s">
         <v>892</v>
       </c>
       <c r="K480" s="1" t="s">
@@ -20993,7 +21402,7 @@
       <c r="I481" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J481" s="74" t="s">
+      <c r="J481" s="70" t="s">
         <v>894</v>
       </c>
       <c r="K481" s="1" t="s">
@@ -21027,7 +21436,7 @@
       <c r="I482" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J482" s="74" t="s">
+      <c r="J482" s="70" t="s">
         <v>897</v>
       </c>
       <c r="K482" s="1" t="s">
@@ -21063,7 +21472,7 @@
       <c r="I483" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J483" s="77" t="s">
+      <c r="J483" s="73" t="s">
         <v>33</v>
       </c>
       <c r="K483" s="1" t="s">
@@ -21099,7 +21508,7 @@
       <c r="I484" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J484" s="74" t="s">
+      <c r="J484" s="70" t="s">
         <v>899</v>
       </c>
       <c r="K484" s="1" t="s">
@@ -21135,7 +21544,7 @@
       <c r="I485" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="J485" s="78" t="s">
+      <c r="J485" s="74" t="s">
         <v>901</v>
       </c>
       <c r="K485" s="1" t="s">
@@ -21171,7 +21580,7 @@
       <c r="I486" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J486" s="74" t="s">
+      <c r="J486" s="70" t="s">
         <v>902</v>
       </c>
       <c r="K486" s="1" t="s">
@@ -21207,7 +21616,7 @@
       <c r="I487" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J487" s="74" t="s">
+      <c r="J487" s="70" t="s">
         <v>903</v>
       </c>
       <c r="K487" s="1" t="s">
@@ -21243,7 +21652,7 @@
       <c r="I488" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J488" s="74" t="s">
+      <c r="J488" s="70" t="s">
         <v>906</v>
       </c>
       <c r="K488" s="1" t="s">
@@ -21279,7 +21688,7 @@
       <c r="I489" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J489" s="74" t="s">
+      <c r="J489" s="70" t="s">
         <v>908</v>
       </c>
       <c r="K489" s="1" t="s">
@@ -21315,7 +21724,7 @@
       <c r="I490" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J490" s="74" t="s">
+      <c r="J490" s="70" t="s">
         <v>911</v>
       </c>
       <c r="K490" s="1" t="s">
@@ -21351,7 +21760,7 @@
       <c r="I491" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J491" s="74" t="s">
+      <c r="J491" s="70" t="s">
         <v>912</v>
       </c>
       <c r="K491" s="1" t="s">
@@ -21387,7 +21796,7 @@
       <c r="I492" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J492" s="74" t="s">
+      <c r="J492" s="70" t="s">
         <v>913</v>
       </c>
       <c r="K492" s="1" t="s">
@@ -21423,7 +21832,7 @@
       <c r="I493" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J493" s="74" t="s">
+      <c r="J493" s="70" t="s">
         <v>914</v>
       </c>
       <c r="K493" s="1" t="s">
@@ -21459,7 +21868,7 @@
       <c r="I494" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J494" s="77" t="s">
+      <c r="J494" s="73" t="s">
         <v>687</v>
       </c>
       <c r="K494" s="1" t="s">
@@ -21495,7 +21904,7 @@
       <c r="I495" s="38" t="s">
         <v>852</v>
       </c>
-      <c r="J495" s="75" t="s">
+      <c r="J495" s="71" t="s">
         <v>915</v>
       </c>
       <c r="K495" s="1" t="s">
@@ -21504,1842 +21913,2669 @@
     </row>
     <row r="496" spans="1:11">
       <c r="A496" s="26">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B496" s="27" t="str">
         <f t="shared" si="44"/>
-        <v>火</v>
+        <v>月</v>
       </c>
       <c r="C496" s="28" t="s">
-        <v>501</v>
+        <v>391</v>
       </c>
       <c r="D496" s="28" t="s">
-        <v>29</v>
+        <v>151</v>
       </c>
       <c r="E496" s="29">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F496" s="30" t="s">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="G496" s="30" t="s">
-        <v>10</v>
+        <v>934</v>
       </c>
       <c r="H496" s="31">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="I496" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="J496" s="77" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="J496" s="73" t="s">
+        <v>931</v>
       </c>
       <c r="K496" s="1" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="497" spans="1:12">
+    <row r="497" spans="1:11">
       <c r="A497" s="26">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B497" s="27" t="str">
         <f t="shared" si="44"/>
-        <v>火</v>
+        <v>月</v>
       </c>
       <c r="C497" s="28" t="s">
         <v>602</v>
       </c>
       <c r="D497" s="28" t="s">
-        <v>809</v>
+        <v>155</v>
       </c>
       <c r="E497" s="29">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F497" s="30" t="s">
-        <v>402</v>
+        <v>13</v>
       </c>
       <c r="G497" s="30" t="s">
-        <v>916</v>
+        <v>932</v>
       </c>
       <c r="H497" s="31">
         <v>0</v>
       </c>
       <c r="I497" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="J497" s="74" t="s">
-        <v>917</v>
+        <v>9</v>
+      </c>
+      <c r="J497" s="73" t="s">
+        <v>933</v>
       </c>
       <c r="K497" s="1" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="498" spans="1:12">
+    <row r="498" spans="1:11">
       <c r="A498" s="26">
         <v>46294</v>
       </c>
       <c r="B498" s="27" t="str">
+        <f t="shared" ref="B498:B499" si="45">TEXT(A498,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="C498" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="D498" s="28" t="s">
+        <v>935</v>
+      </c>
+      <c r="E498" s="29">
+        <v>20</v>
+      </c>
+      <c r="F498" s="30" t="s">
+        <v>936</v>
+      </c>
+      <c r="G498" s="30" t="s">
+        <v>929</v>
+      </c>
+      <c r="H498" s="31">
+        <v>2500</v>
+      </c>
+      <c r="I498" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J498" s="73" t="s">
+        <v>937</v>
+      </c>
+      <c r="K498" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="499" spans="1:11">
+      <c r="A499" s="26">
+        <v>46294</v>
+      </c>
+      <c r="B499" s="27" t="str">
+        <f t="shared" si="45"/>
+        <v>火</v>
+      </c>
+      <c r="C499" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="D499" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="E499" s="29">
+        <v>12</v>
+      </c>
+      <c r="F499" s="30" t="s">
+        <v>938</v>
+      </c>
+      <c r="G499" s="30" t="s">
+        <v>939</v>
+      </c>
+      <c r="H499" s="31">
+        <v>2000</v>
+      </c>
+      <c r="I499" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J499" s="73" t="s">
+        <v>940</v>
+      </c>
+      <c r="K499" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="500" spans="1:11">
+      <c r="A500" s="26">
+        <v>46294</v>
+      </c>
+      <c r="B500" s="27" t="str">
+        <f t="shared" ref="B500" si="46">TEXT(A500,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="C500" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="D500" s="28" t="s">
+        <v>941</v>
+      </c>
+      <c r="E500" s="29">
+        <v>20</v>
+      </c>
+      <c r="F500" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="G500" s="30" t="s">
+        <v>943</v>
+      </c>
+      <c r="H500" s="31">
+        <v>0</v>
+      </c>
+      <c r="I500" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J500" s="73" t="s">
+        <v>942</v>
+      </c>
+      <c r="K500" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="501" spans="1:11">
+      <c r="A501" s="26">
+        <v>46294</v>
+      </c>
+      <c r="B501" s="27" t="str">
         <f t="shared" si="44"/>
         <v>火</v>
       </c>
-      <c r="C498" s="28" t="s">
-        <v>544</v>
-      </c>
-      <c r="D498" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="E498" s="29">
-        <v>30</v>
-      </c>
-      <c r="F498" s="30" t="s">
-        <v>538</v>
-      </c>
-      <c r="G498" s="30" t="s">
-        <v>857</v>
-      </c>
-      <c r="H498" s="31">
+      <c r="C501" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="D501" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E501" s="29">
+        <v>40</v>
+      </c>
+      <c r="F501" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="G501" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H501" s="31">
         <v>3000</v>
       </c>
-      <c r="I498" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="J498" s="74" t="s">
-        <v>918</v>
-      </c>
-      <c r="K498" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="499" spans="1:12">
-      <c r="A499" s="26">
+      <c r="I501" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J501" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="K501" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="502" spans="1:11">
+      <c r="A502" s="26">
         <v>46294</v>
       </c>
-      <c r="B499" s="27" t="str">
+      <c r="B502" s="27" t="str">
         <f t="shared" si="44"/>
         <v>火</v>
       </c>
-      <c r="C499" s="28" t="s">
-        <v>705</v>
-      </c>
-      <c r="D499" s="28" t="s">
-        <v>706</v>
-      </c>
-      <c r="E499" s="29">
+      <c r="C502" s="28" t="s">
+        <v>602</v>
+      </c>
+      <c r="D502" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E502" s="29">
         <v>20</v>
       </c>
-      <c r="F499" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G499" s="30" t="s">
-        <v>707</v>
-      </c>
-      <c r="H499" s="31">
-        <v>0</v>
-      </c>
-      <c r="I499" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="J499" s="74" t="s">
-        <v>919</v>
-      </c>
-      <c r="K499" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="500" spans="1:12" ht="18.45">
-      <c r="A500" s="26">
-        <v>46301</v>
-      </c>
-      <c r="B500" s="27" t="str">
-        <f>TEXT(A500,"aaa")</f>
+      <c r="F502" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="G502" s="30" t="s">
+        <v>703</v>
+      </c>
+      <c r="H502" s="31">
+        <v>2200</v>
+      </c>
+      <c r="I502" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J502" s="73" t="s">
+        <v>944</v>
+      </c>
+      <c r="K502" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="503" spans="1:11">
+      <c r="A503" s="26">
+        <v>46294</v>
+      </c>
+      <c r="B503" s="27" t="str">
+        <f t="shared" si="44"/>
         <v>火</v>
       </c>
-      <c r="C500" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="D500" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="E500" s="12"/>
-      <c r="F500" s="13" t="s">
-        <v>608</v>
-      </c>
-      <c r="G500" s="13" t="s">
-        <v>609</v>
-      </c>
-      <c r="H500" s="14">
-        <v>0</v>
-      </c>
-      <c r="I500" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J500" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K500" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="501" spans="1:12">
-      <c r="A501" s="26">
-        <v>46308</v>
-      </c>
-      <c r="B501" s="27" t="str">
-        <f t="shared" ref="B501:B518" si="45">TEXT(A501,"aaa")</f>
+      <c r="C503" s="28" t="s">
+        <v>602</v>
+      </c>
+      <c r="D503" s="28" t="s">
+        <v>809</v>
+      </c>
+      <c r="E503" s="29">
+        <v>100</v>
+      </c>
+      <c r="F503" s="30" t="s">
+        <v>402</v>
+      </c>
+      <c r="G503" s="30" t="s">
+        <v>916</v>
+      </c>
+      <c r="H503" s="31">
+        <v>0</v>
+      </c>
+      <c r="I503" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="J503" s="70" t="s">
+        <v>917</v>
+      </c>
+      <c r="K503" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="504" spans="1:11">
+      <c r="A504" s="26">
+        <v>46294</v>
+      </c>
+      <c r="B504" s="27" t="str">
+        <f t="shared" si="44"/>
         <v>火</v>
       </c>
-      <c r="C501" s="28" t="s">
-        <v>705</v>
-      </c>
-      <c r="D501" s="28" t="s">
-        <v>706</v>
-      </c>
-      <c r="E501" s="29">
-        <v>30</v>
-      </c>
-      <c r="F501" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G501" s="30" t="s">
-        <v>707</v>
-      </c>
-      <c r="H501" s="31">
-        <v>0</v>
-      </c>
-      <c r="I501" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="J501" s="74" t="s">
-        <v>920</v>
-      </c>
-      <c r="K501" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="502" spans="1:12">
-      <c r="A502" s="26">
-        <v>46309</v>
-      </c>
-      <c r="B502" s="27" t="str">
-        <f t="shared" si="45"/>
-        <v>水</v>
-      </c>
-      <c r="C502" s="28" t="s">
-        <v>921</v>
-      </c>
-      <c r="D502" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="E502" s="29">
+      <c r="C504" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D504" s="28" t="s">
+        <v>406</v>
+      </c>
+      <c r="E504" s="29">
         <v>40</v>
       </c>
-      <c r="F502" s="30" t="s">
-        <v>922</v>
-      </c>
-      <c r="G502" s="30" t="s">
-        <v>923</v>
-      </c>
-      <c r="H502" s="33">
-        <v>1500</v>
-      </c>
-      <c r="I502" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="J502" s="74" t="s">
-        <v>924</v>
-      </c>
-      <c r="K502" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="503" spans="1:12">
-      <c r="A503" s="26">
-        <v>46315</v>
-      </c>
-      <c r="B503" s="27" t="str">
-        <f t="shared" si="45"/>
+      <c r="F504" s="30" t="s">
+        <v>945</v>
+      </c>
+      <c r="G504" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="H504" s="31">
+        <v>0</v>
+      </c>
+      <c r="I504" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J504" s="73" t="s">
+        <v>946</v>
+      </c>
+      <c r="K504" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="505" spans="1:11">
+      <c r="A505" s="26">
+        <v>46294</v>
+      </c>
+      <c r="B505" s="27" t="str">
+        <f t="shared" si="44"/>
         <v>火</v>
       </c>
-      <c r="C503" s="28" t="s">
-        <v>848</v>
-      </c>
-      <c r="D503" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E503" s="29">
-        <v>50</v>
-      </c>
-      <c r="F503" s="30" t="s">
-        <v>377</v>
-      </c>
-      <c r="G503" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H503" s="31">
-        <v>3000</v>
-      </c>
-      <c r="I503" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="J503" s="77" t="s">
-        <v>687</v>
-      </c>
-      <c r="K503" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="504" spans="1:12">
-      <c r="A504" s="26">
-        <v>46317</v>
-      </c>
-      <c r="B504" s="27" t="str">
-        <f t="shared" si="45"/>
-        <v>木</v>
-      </c>
-      <c r="C504" s="38" t="s">
-        <v>925</v>
-      </c>
-      <c r="D504" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="E504" s="39">
-        <v>30</v>
-      </c>
-      <c r="F504" s="40" t="s">
-        <v>565</v>
-      </c>
-      <c r="G504" s="40" t="s">
-        <v>640</v>
-      </c>
-      <c r="H504" s="32">
-        <v>3000</v>
-      </c>
-      <c r="I504" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="J504" s="74" t="s">
-        <v>926</v>
-      </c>
-      <c r="K504" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="505" spans="1:12">
-      <c r="A505" s="26">
-        <v>46324</v>
-      </c>
-      <c r="B505" s="27" t="str">
-        <f t="shared" si="45"/>
-        <v>木</v>
-      </c>
       <c r="C505" s="28" t="s">
-        <v>705</v>
+        <v>544</v>
       </c>
       <c r="D505" s="28" t="s">
-        <v>706</v>
+        <v>263</v>
       </c>
       <c r="E505" s="29">
         <v>30</v>
       </c>
       <c r="F505" s="30" t="s">
+        <v>538</v>
+      </c>
+      <c r="G505" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="H505" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I505" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J505" s="70" t="s">
+        <v>918</v>
+      </c>
+      <c r="K505" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="506" spans="1:11">
+      <c r="A506" s="26">
+        <v>46294</v>
+      </c>
+      <c r="B506" s="27" t="str">
+        <f t="shared" si="44"/>
+        <v>火</v>
+      </c>
+      <c r="C506" s="28" t="s">
+        <v>705</v>
+      </c>
+      <c r="D506" s="28" t="s">
+        <v>706</v>
+      </c>
+      <c r="E506" s="29">
+        <v>20</v>
+      </c>
+      <c r="F506" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="G505" s="30" t="s">
+      <c r="G506" s="30" t="s">
         <v>707</v>
       </c>
-      <c r="H505" s="31">
-        <v>0</v>
-      </c>
-      <c r="I505" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="J505" s="74" t="s">
+      <c r="H506" s="31">
+        <v>0</v>
+      </c>
+      <c r="I506" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J506" s="70" t="s">
+        <v>919</v>
+      </c>
+      <c r="K506" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="507" spans="1:11">
+      <c r="A507" s="26">
+        <v>46295</v>
+      </c>
+      <c r="B507" s="27" t="str">
+        <f t="shared" si="44"/>
+        <v>水</v>
+      </c>
+      <c r="C507" s="28" t="s">
+        <v>551</v>
+      </c>
+      <c r="D507" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="E507" s="29">
+        <v>12</v>
+      </c>
+      <c r="F507" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="G507" s="30" t="s">
+        <v>939</v>
+      </c>
+      <c r="H507" s="31">
+        <v>2000</v>
+      </c>
+      <c r="I507" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J507" s="73" t="s">
+        <v>947</v>
+      </c>
+      <c r="K507" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="508" spans="1:11">
+      <c r="A508" s="26">
+        <v>46295</v>
+      </c>
+      <c r="B508" s="27" t="str">
+        <f t="shared" ref="B508:B513" si="47">TEXT(A508,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="C508" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D508" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E508" s="29">
+        <v>80</v>
+      </c>
+      <c r="F508" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="G508" s="30" t="s">
+        <v>948</v>
+      </c>
+      <c r="H508" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I508" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J508" s="73" t="s">
+        <v>949</v>
+      </c>
+      <c r="K508" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="509" spans="1:11">
+      <c r="A509" s="26">
+        <v>46296</v>
+      </c>
+      <c r="B509" s="27" t="str">
+        <f t="shared" si="47"/>
+        <v>木</v>
+      </c>
+      <c r="C509" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D509" s="28" t="s">
+        <v>706</v>
+      </c>
+      <c r="E509" s="29">
+        <v>70</v>
+      </c>
+      <c r="F509" s="30" t="s">
+        <v>950</v>
+      </c>
+      <c r="G509" s="30" t="s">
+        <v>730</v>
+      </c>
+      <c r="H509" s="31">
+        <v>0</v>
+      </c>
+      <c r="I509" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J509" s="73" t="s">
+        <v>951</v>
+      </c>
+      <c r="K509" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="510" spans="1:11">
+      <c r="A510" s="26">
+        <v>46297</v>
+      </c>
+      <c r="B510" s="27" t="str">
+        <f t="shared" si="47"/>
+        <v>金</v>
+      </c>
+      <c r="C510" s="28" t="s">
+        <v>351</v>
+      </c>
+      <c r="D510" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="E510" s="29">
+        <v>50</v>
+      </c>
+      <c r="F510" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G510" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H510" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I510" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J510" s="73" t="s">
+        <v>952</v>
+      </c>
+      <c r="K510" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="511" spans="1:11">
+      <c r="A511" s="26">
+        <v>46301</v>
+      </c>
+      <c r="B511" s="27" t="str">
+        <f t="shared" ref="B511" si="48">TEXT(A511,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="C511" s="28" t="s">
+        <v>627</v>
+      </c>
+      <c r="D511" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="E511" s="29">
+        <v>50</v>
+      </c>
+      <c r="F511" s="30" t="s">
+        <v>447</v>
+      </c>
+      <c r="G511" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H511" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I511" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J511" s="73" t="s">
+        <v>953</v>
+      </c>
+      <c r="K511" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="512" spans="1:11">
+      <c r="A512" s="26">
+        <v>46301</v>
+      </c>
+      <c r="B512" s="27" t="str">
+        <f t="shared" si="47"/>
+        <v>火</v>
+      </c>
+      <c r="C512" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D512" s="28" t="s">
+        <v>954</v>
+      </c>
+      <c r="E512" s="29">
+        <v>70</v>
+      </c>
+      <c r="F512" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G512" s="30" t="s">
+        <v>730</v>
+      </c>
+      <c r="H512" s="31">
+        <v>0</v>
+      </c>
+      <c r="I512" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J512" s="73" t="s">
+        <v>955</v>
+      </c>
+      <c r="K512" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="513" spans="1:11">
+      <c r="A513" s="26">
+        <v>46301</v>
+      </c>
+      <c r="B513" s="27" t="str">
+        <f t="shared" si="47"/>
+        <v>火</v>
+      </c>
+      <c r="C513" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D513" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E513" s="29">
+        <v>50</v>
+      </c>
+      <c r="F513" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="G513" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="H513" s="31">
+        <v>0</v>
+      </c>
+      <c r="I513" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J513" s="73" t="s">
+        <v>956</v>
+      </c>
+      <c r="K513" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="514" spans="1:11" ht="18.45">
+      <c r="A514" s="26">
+        <v>46301</v>
+      </c>
+      <c r="B514" s="27" t="str">
+        <f>TEXT(A514,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="C514" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D514" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="E514" s="12"/>
+      <c r="F514" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="G514" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="H514" s="14">
+        <v>0</v>
+      </c>
+      <c r="I514" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J514" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K514" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="515" spans="1:11">
+      <c r="A515" s="26">
+        <v>46302</v>
+      </c>
+      <c r="B515" s="27" t="str">
+        <f>TEXT(A515,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="C515" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="D515" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="E515" s="29">
+        <v>25</v>
+      </c>
+      <c r="F515" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="G515" s="30" t="s">
+        <v>957</v>
+      </c>
+      <c r="H515" s="31">
+        <v>2000</v>
+      </c>
+      <c r="I515" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J515" s="73" t="s">
+        <v>958</v>
+      </c>
+      <c r="K515" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="516" spans="1:11">
+      <c r="A516" s="26">
+        <v>46302</v>
+      </c>
+      <c r="B516" s="27" t="str">
+        <f t="shared" ref="B516" si="49">TEXT(A516,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="C516" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="D516" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E516" s="29">
+        <v>30</v>
+      </c>
+      <c r="F516" s="30" t="s">
+        <v>842</v>
+      </c>
+      <c r="G516" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="H516" s="31">
+        <v>0</v>
+      </c>
+      <c r="I516" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J516" s="73" t="s">
+        <v>959</v>
+      </c>
+      <c r="K516" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="517" spans="1:11">
+      <c r="A517" s="26">
+        <v>46302</v>
+      </c>
+      <c r="B517" s="27" t="str">
+        <f>TEXT(A517,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="C517" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="D517" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="E517" s="29">
+        <v>30</v>
+      </c>
+      <c r="F517" s="30" t="s">
+        <v>634</v>
+      </c>
+      <c r="G517" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H517" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I517" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J517" s="73" t="s">
+        <v>960</v>
+      </c>
+      <c r="K517" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="518" spans="1:11">
+      <c r="A518" s="26">
+        <v>46302</v>
+      </c>
+      <c r="B518" s="27" t="str">
+        <f t="shared" ref="B518" si="50">TEXT(A518,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="C518" s="28" t="s">
+        <v>507</v>
+      </c>
+      <c r="D518" s="28" t="s">
+        <v>428</v>
+      </c>
+      <c r="E518" s="29">
+        <v>50</v>
+      </c>
+      <c r="F518" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G518" s="30" t="s">
+        <v>961</v>
+      </c>
+      <c r="H518" s="31">
+        <v>1000</v>
+      </c>
+      <c r="I518" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J518" s="73" t="s">
+        <v>962</v>
+      </c>
+      <c r="K518" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="519" spans="1:11">
+      <c r="A519" s="26">
+        <v>46302</v>
+      </c>
+      <c r="B519" s="27" t="str">
+        <f>TEXT(A519,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="C519" s="28" t="s">
+        <v>507</v>
+      </c>
+      <c r="D519" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E519" s="29">
+        <v>30</v>
+      </c>
+      <c r="F519" s="30" t="s">
+        <v>963</v>
+      </c>
+      <c r="G519" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="H519" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I519" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J519" s="73" t="s">
+        <v>964</v>
+      </c>
+      <c r="K519" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="520" spans="1:11">
+      <c r="A520" s="26">
+        <v>46303</v>
+      </c>
+      <c r="B520" s="27" t="str">
+        <f t="shared" ref="B520" si="51">TEXT(A520,"aaa")</f>
+        <v>木</v>
+      </c>
+      <c r="C520" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="D520" s="28" t="s">
+        <v>935</v>
+      </c>
+      <c r="E520" s="29">
+        <v>15</v>
+      </c>
+      <c r="F520" s="30" t="s">
+        <v>965</v>
+      </c>
+      <c r="G520" s="30" t="s">
+        <v>929</v>
+      </c>
+      <c r="H520" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I520" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J520" s="73" t="s">
+        <v>966</v>
+      </c>
+      <c r="K520" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="521" spans="1:11">
+      <c r="A521" s="26">
+        <v>46303</v>
+      </c>
+      <c r="B521" s="27" t="str">
+        <f>TEXT(A521,"aaa")</f>
+        <v>木</v>
+      </c>
+      <c r="C521" s="28" t="s">
+        <v>712</v>
+      </c>
+      <c r="D521" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E521" s="29">
+        <v>20</v>
+      </c>
+      <c r="F521" s="30" t="s">
+        <v>402</v>
+      </c>
+      <c r="G521" s="30" t="s">
+        <v>875</v>
+      </c>
+      <c r="H521" s="31">
+        <v>0</v>
+      </c>
+      <c r="I521" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J521" s="73" t="s">
+        <v>967</v>
+      </c>
+      <c r="K521" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="522" spans="1:11">
+      <c r="A522" s="26">
+        <v>46303</v>
+      </c>
+      <c r="B522" s="27" t="str">
+        <f t="shared" ref="B522" si="52">TEXT(A522,"aaa")</f>
+        <v>木</v>
+      </c>
+      <c r="C522" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="D522" s="28" t="s">
+        <v>968</v>
+      </c>
+      <c r="E522" s="29">
+        <v>50</v>
+      </c>
+      <c r="F522" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G522" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="H522" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I522" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J522" s="73" t="s">
+        <v>969</v>
+      </c>
+      <c r="K522" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="523" spans="1:11">
+      <c r="A523" s="26">
+        <v>46303</v>
+      </c>
+      <c r="B523" s="27" t="str">
+        <f>TEXT(A523,"aaa")</f>
+        <v>木</v>
+      </c>
+      <c r="C523" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D523" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="E523" s="29">
+        <v>70</v>
+      </c>
+      <c r="F523" s="30" t="s">
+        <v>970</v>
+      </c>
+      <c r="G523" s="30" t="s">
+        <v>971</v>
+      </c>
+      <c r="H523" s="31">
+        <v>0</v>
+      </c>
+      <c r="I523" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J523" s="73" t="s">
+        <v>972</v>
+      </c>
+      <c r="K523" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="524" spans="1:11">
+      <c r="A524" s="26">
+        <v>46303</v>
+      </c>
+      <c r="B524" s="27" t="str">
+        <f t="shared" ref="B524:B530" si="53">TEXT(A524,"aaa")</f>
+        <v>木</v>
+      </c>
+      <c r="C524" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="D524" s="28" t="s">
+        <v>718</v>
+      </c>
+      <c r="E524" s="29"/>
+      <c r="F524" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="G524" s="30" t="s">
+        <v>609</v>
+      </c>
+      <c r="H524" s="31">
+        <v>0</v>
+      </c>
+      <c r="I524" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J524" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="K524" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="525" spans="1:11">
+      <c r="A525" s="26">
+        <v>46304</v>
+      </c>
+      <c r="B525" s="27" t="str">
+        <f t="shared" ref="B525:B527" si="54">TEXT(A525,"aaa")</f>
+        <v>金</v>
+      </c>
+      <c r="C525" s="28" t="s">
+        <v>973</v>
+      </c>
+      <c r="D525" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E525" s="29">
+        <v>45</v>
+      </c>
+      <c r="F525" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="G525" s="30" t="s">
+        <v>974</v>
+      </c>
+      <c r="H525" s="31">
+        <v>0</v>
+      </c>
+      <c r="I525" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J525" s="73" t="s">
+        <v>975</v>
+      </c>
+      <c r="K525" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="526" spans="1:11">
+      <c r="A526" s="26">
+        <v>46304</v>
+      </c>
+      <c r="B526" s="27" t="str">
+        <f t="shared" ref="B526" si="55">TEXT(A526,"aaa")</f>
+        <v>金</v>
+      </c>
+      <c r="C526" s="28" t="s">
+        <v>449</v>
+      </c>
+      <c r="D526" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E526" s="29">
+        <v>50</v>
+      </c>
+      <c r="F526" s="30" t="s">
+        <v>976</v>
+      </c>
+      <c r="G526" s="30" t="s">
+        <v>977</v>
+      </c>
+      <c r="H526" s="31">
+        <v>0</v>
+      </c>
+      <c r="I526" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J526" s="73" t="s">
+        <v>978</v>
+      </c>
+      <c r="K526" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="527" spans="1:11">
+      <c r="A527" s="26">
+        <v>46304</v>
+      </c>
+      <c r="B527" s="27" t="str">
+        <f t="shared" si="54"/>
+        <v>金</v>
+      </c>
+      <c r="C527" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="D527" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E527" s="29">
+        <v>60</v>
+      </c>
+      <c r="F527" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G527" s="30" t="s">
+        <v>930</v>
+      </c>
+      <c r="H527" s="31">
+        <v>0</v>
+      </c>
+      <c r="I527" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J527" s="73" t="s">
+        <v>979</v>
+      </c>
+      <c r="K527" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="528" spans="1:11">
+      <c r="A528" s="26">
+        <v>46304</v>
+      </c>
+      <c r="B528" s="27" t="str">
+        <f t="shared" si="53"/>
+        <v>金</v>
+      </c>
+      <c r="C528" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="D528" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="E528" s="29">
+        <v>30</v>
+      </c>
+      <c r="F528" s="30" t="s">
+        <v>980</v>
+      </c>
+      <c r="G528" s="30" t="s">
+        <v>981</v>
+      </c>
+      <c r="H528" s="31">
+        <v>2000</v>
+      </c>
+      <c r="I528" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J528" s="73" t="s">
+        <v>982</v>
+      </c>
+      <c r="K528" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="529" spans="1:11">
+      <c r="A529" s="26">
+        <v>46305</v>
+      </c>
+      <c r="B529" s="27" t="str">
+        <f t="shared" si="53"/>
+        <v>土</v>
+      </c>
+      <c r="C529" s="28" t="s">
+        <v>983</v>
+      </c>
+      <c r="D529" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E529" s="29">
+        <v>15</v>
+      </c>
+      <c r="F529" s="28" t="s">
+        <v>986</v>
+      </c>
+      <c r="G529" s="30" t="s">
+        <v>984</v>
+      </c>
+      <c r="H529" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I529" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J529" s="73" t="s">
+        <v>985</v>
+      </c>
+      <c r="K529" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="530" spans="1:11">
+      <c r="A530" s="26">
+        <v>46308</v>
+      </c>
+      <c r="B530" s="27" t="str">
+        <f t="shared" si="53"/>
+        <v>火</v>
+      </c>
+      <c r="C530" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D530" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="E530" s="29">
+        <v>30</v>
+      </c>
+      <c r="F530" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="G530" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="H530" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I530" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J530" s="73" t="s">
+        <v>987</v>
+      </c>
+      <c r="K530" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="531" spans="1:11">
+      <c r="A531" s="26">
+        <v>46308</v>
+      </c>
+      <c r="B531" s="27" t="str">
+        <f t="shared" ref="B531:B581" si="56">TEXT(A531,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="C531" s="28" t="s">
+        <v>705</v>
+      </c>
+      <c r="D531" s="28" t="s">
+        <v>706</v>
+      </c>
+      <c r="E531" s="29">
+        <v>30</v>
+      </c>
+      <c r="F531" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G531" s="30" t="s">
+        <v>707</v>
+      </c>
+      <c r="H531" s="31">
+        <v>0</v>
+      </c>
+      <c r="I531" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J531" s="70" t="s">
+        <v>920</v>
+      </c>
+      <c r="K531" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="532" spans="1:11">
+      <c r="A532" s="26">
+        <v>46309</v>
+      </c>
+      <c r="B532" s="27" t="str">
+        <f t="shared" ref="B532" si="57">TEXT(A532,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="C532" s="28" t="s">
+        <v>449</v>
+      </c>
+      <c r="D532" s="28" t="s">
+        <v>988</v>
+      </c>
+      <c r="E532" s="29">
+        <v>80</v>
+      </c>
+      <c r="F532" s="28" t="s">
+        <v>989</v>
+      </c>
+      <c r="G532" s="30" t="s">
+        <v>990</v>
+      </c>
+      <c r="H532" s="31">
+        <v>1000</v>
+      </c>
+      <c r="I532" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J532" s="73" t="s">
+        <v>991</v>
+      </c>
+      <c r="K532" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="533" spans="1:11">
+      <c r="A533" s="26">
+        <v>46309</v>
+      </c>
+      <c r="B533" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>水</v>
+      </c>
+      <c r="C533" s="28" t="s">
+        <v>921</v>
+      </c>
+      <c r="D533" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E533" s="29">
+        <v>40</v>
+      </c>
+      <c r="F533" s="30" t="s">
+        <v>922</v>
+      </c>
+      <c r="G533" s="30" t="s">
+        <v>923</v>
+      </c>
+      <c r="H533" s="33">
+        <v>1500</v>
+      </c>
+      <c r="I533" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J533" s="70" t="s">
+        <v>924</v>
+      </c>
+      <c r="K533" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="534" spans="1:11">
+      <c r="A534" s="26">
+        <v>46309</v>
+      </c>
+      <c r="B534" s="27" t="str">
+        <f t="shared" ref="B534" si="58">TEXT(A534,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="C534" s="28" t="s">
+        <v>610</v>
+      </c>
+      <c r="D534" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="E534" s="29">
+        <v>30</v>
+      </c>
+      <c r="F534" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G534" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="H534" s="31">
+        <v>0</v>
+      </c>
+      <c r="I534" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J534" s="73" t="s">
+        <v>36</v>
+      </c>
+      <c r="K534" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="535" spans="1:11">
+      <c r="A535" s="26">
+        <v>46309</v>
+      </c>
+      <c r="B535" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>水</v>
+      </c>
+      <c r="C535" s="28" t="s">
+        <v>382</v>
+      </c>
+      <c r="D535" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="E535" s="29">
+        <v>50</v>
+      </c>
+      <c r="F535" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G535" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="H535" s="31">
+        <v>1000</v>
+      </c>
+      <c r="I535" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J535" s="73" t="s">
+        <v>992</v>
+      </c>
+      <c r="K535" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="536" spans="1:11">
+      <c r="A536" s="26">
+        <v>46309</v>
+      </c>
+      <c r="B536" s="27" t="str">
+        <f t="shared" ref="B536:B545" si="59">TEXT(A536,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="C536" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="D536" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="E536" s="29"/>
+      <c r="F536" s="28" t="s">
+        <v>608</v>
+      </c>
+      <c r="G536" s="30" t="s">
+        <v>609</v>
+      </c>
+      <c r="H536" s="31">
+        <v>0</v>
+      </c>
+      <c r="I536" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J536" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="K536" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="537" spans="1:11">
+      <c r="A537" s="26">
+        <v>46309</v>
+      </c>
+      <c r="B537" s="27" t="str">
+        <f t="shared" si="59"/>
+        <v>水</v>
+      </c>
+      <c r="C537" s="28" t="s">
+        <v>507</v>
+      </c>
+      <c r="D537" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E537" s="29">
+        <v>20</v>
+      </c>
+      <c r="F537" s="28" t="s">
+        <v>842</v>
+      </c>
+      <c r="G537" s="30" t="s">
+        <v>844</v>
+      </c>
+      <c r="H537" s="31">
+        <v>0</v>
+      </c>
+      <c r="I537" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J537" s="73" t="s">
+        <v>993</v>
+      </c>
+      <c r="K537" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="538" spans="1:11">
+      <c r="A538" s="26">
+        <v>46310</v>
+      </c>
+      <c r="B538" s="27" t="str">
+        <f t="shared" si="59"/>
+        <v>木</v>
+      </c>
+      <c r="C538" s="28" t="s">
+        <v>422</v>
+      </c>
+      <c r="D538" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E538" s="29">
+        <v>65</v>
+      </c>
+      <c r="F538" s="28" t="s">
+        <v>402</v>
+      </c>
+      <c r="G538" s="30" t="s">
+        <v>998</v>
+      </c>
+      <c r="H538" s="31">
+        <v>0</v>
+      </c>
+      <c r="I538" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J538" s="73" t="s">
+        <v>994</v>
+      </c>
+      <c r="K538" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="539" spans="1:11">
+      <c r="A539" s="26">
+        <v>46310</v>
+      </c>
+      <c r="B539" s="27" t="str">
+        <f t="shared" ref="B539" si="60">TEXT(A539,"aaa")</f>
+        <v>木</v>
+      </c>
+      <c r="C539" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="D539" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="E539" s="29">
+        <v>50</v>
+      </c>
+      <c r="F539" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="G539" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H539" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I539" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J539" s="73" t="s">
+        <v>995</v>
+      </c>
+      <c r="K539" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="540" spans="1:11">
+      <c r="A540" s="26">
+        <v>46310</v>
+      </c>
+      <c r="B540" s="27" t="str">
+        <f t="shared" si="59"/>
+        <v>木</v>
+      </c>
+      <c r="C540" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D540" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="E540" s="29">
+        <v>70</v>
+      </c>
+      <c r="F540" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="G540" s="30" t="s">
+        <v>996</v>
+      </c>
+      <c r="H540" s="31">
+        <v>0</v>
+      </c>
+      <c r="I540" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J540" s="73" t="s">
+        <v>997</v>
+      </c>
+      <c r="K540" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="541" spans="1:11">
+      <c r="A541" s="26">
+        <v>46310</v>
+      </c>
+      <c r="B541" s="27" t="str">
+        <f t="shared" ref="B541:B544" si="61">TEXT(A541,"aaa")</f>
+        <v>木</v>
+      </c>
+      <c r="C541" s="28" t="s">
+        <v>787</v>
+      </c>
+      <c r="D541" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E541" s="29">
+        <v>85</v>
+      </c>
+      <c r="F541" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G541" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="H541" s="31">
+        <v>0</v>
+      </c>
+      <c r="I541" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J541" s="73" t="s">
+        <v>36</v>
+      </c>
+      <c r="K541" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="542" spans="1:11">
+      <c r="A542" s="26">
+        <v>46312</v>
+      </c>
+      <c r="B542" s="27" t="str">
+        <f t="shared" si="61"/>
+        <v>土</v>
+      </c>
+      <c r="C542" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="D542" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="E542" s="29"/>
+      <c r="F542" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="G542" s="30" t="s">
+        <v>609</v>
+      </c>
+      <c r="H542" s="31">
+        <v>0</v>
+      </c>
+      <c r="I542" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J542" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="K542" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="543" spans="1:11">
+      <c r="A543" s="26">
+        <v>46313</v>
+      </c>
+      <c r="B543" s="27" t="str">
+        <f t="shared" ref="B543" si="62">TEXT(A543,"aaa")</f>
+        <v>日</v>
+      </c>
+      <c r="C543" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="D543" s="28" t="s">
+        <v>558</v>
+      </c>
+      <c r="E543" s="29"/>
+      <c r="F543" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="G543" s="30" t="s">
+        <v>609</v>
+      </c>
+      <c r="H543" s="31">
+        <v>0</v>
+      </c>
+      <c r="I543" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J543" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="K543" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="544" spans="1:11">
+      <c r="A544" s="26">
+        <v>46314</v>
+      </c>
+      <c r="B544" s="27" t="str">
+        <f t="shared" si="61"/>
+        <v>月</v>
+      </c>
+      <c r="C544" s="28" t="s">
+        <v>412</v>
+      </c>
+      <c r="D544" s="28" t="s">
+        <v>354</v>
+      </c>
+      <c r="E544" s="29"/>
+      <c r="F544" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="G544" s="30" t="s">
+        <v>609</v>
+      </c>
+      <c r="H544" s="31">
+        <v>0</v>
+      </c>
+      <c r="I544" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="J544" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="K544" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="545" spans="1:11">
+      <c r="A545" s="26">
+        <v>46314</v>
+      </c>
+      <c r="B545" s="27" t="str">
+        <f t="shared" si="59"/>
+        <v>月</v>
+      </c>
+      <c r="C545" s="28" t="s">
+        <v>999</v>
+      </c>
+      <c r="D545" s="28" t="s">
+        <v>428</v>
+      </c>
+      <c r="E545" s="29">
+        <v>30</v>
+      </c>
+      <c r="F545" s="28" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G545" s="30"/>
+      <c r="H545" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I545" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J545" s="73" t="s">
+        <v>1001</v>
+      </c>
+      <c r="K545" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="546" spans="1:11">
+      <c r="A546" s="26">
+        <v>46315</v>
+      </c>
+      <c r="B546" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>火</v>
+      </c>
+      <c r="C546" s="28" t="s">
+        <v>627</v>
+      </c>
+      <c r="D546" s="28" t="s">
+        <v>748</v>
+      </c>
+      <c r="E546" s="29">
+        <v>70</v>
+      </c>
+      <c r="F546" s="28" t="s">
+        <v>447</v>
+      </c>
+      <c r="G546" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H546" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I546" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J546" s="73" t="s">
+        <v>1002</v>
+      </c>
+      <c r="K546" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="547" spans="1:11">
+      <c r="A547" s="26">
+        <v>46315</v>
+      </c>
+      <c r="B547" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>火</v>
+      </c>
+      <c r="C547" s="28" t="s">
+        <v>848</v>
+      </c>
+      <c r="D547" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E547" s="29">
+        <v>50</v>
+      </c>
+      <c r="F547" s="30" t="s">
+        <v>377</v>
+      </c>
+      <c r="G547" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H547" s="31">
+        <v>3000</v>
+      </c>
+      <c r="I547" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J547" s="73" t="s">
+        <v>687</v>
+      </c>
+      <c r="K547" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="548" spans="1:11">
+      <c r="A548" s="26">
+        <v>46315</v>
+      </c>
+      <c r="B548" s="27" t="str">
+        <f t="shared" ref="B548" si="63">TEXT(A548,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="C548" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="D548" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="E548" s="29">
+        <v>200</v>
+      </c>
+      <c r="F548" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G548" s="30" t="s">
+        <v>641</v>
+      </c>
+      <c r="H548" s="33">
+        <v>0</v>
+      </c>
+      <c r="I548" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J548" s="73" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K548" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="549" spans="1:11">
+      <c r="A549" s="26">
+        <v>46316</v>
+      </c>
+      <c r="B549" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>水</v>
+      </c>
+      <c r="C549" s="28" t="s">
+        <v>351</v>
+      </c>
+      <c r="D549" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E549" s="29">
+        <v>30</v>
+      </c>
+      <c r="F549" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G549" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="H549" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I549" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J549" s="73" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K549" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="550" spans="1:11">
+      <c r="A550" s="26">
+        <v>46316</v>
+      </c>
+      <c r="B550" s="27" t="str">
+        <f t="shared" ref="B550" si="64">TEXT(A550,"aaa")</f>
+        <v>水</v>
+      </c>
+      <c r="C550" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="D550" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E550" s="29">
+        <v>30</v>
+      </c>
+      <c r="F550" s="28" t="s">
+        <v>842</v>
+      </c>
+      <c r="G550" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="H550" s="33">
+        <v>0</v>
+      </c>
+      <c r="I550" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J550" s="73" t="s">
+        <v>1005</v>
+      </c>
+      <c r="K550" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="551" spans="1:11">
+      <c r="A551" s="26">
+        <v>46316</v>
+      </c>
+      <c r="B551" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>水</v>
+      </c>
+      <c r="C551" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="D551" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E551" s="29">
+        <v>45</v>
+      </c>
+      <c r="F551" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="G551" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="H551" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I551" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J551" s="73" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K551" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="552" spans="1:11">
+      <c r="A552" s="26">
+        <v>46316</v>
+      </c>
+      <c r="B552" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>水</v>
+      </c>
+      <c r="C552" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D552" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E552" s="29">
+        <v>70</v>
+      </c>
+      <c r="F552" s="28" t="s">
+        <v>970</v>
+      </c>
+      <c r="G552" s="30" t="s">
+        <v>730</v>
+      </c>
+      <c r="H552" s="33">
+        <v>0</v>
+      </c>
+      <c r="I552" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J552" s="73" t="s">
+        <v>1007</v>
+      </c>
+      <c r="K552" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="553" spans="1:11">
+      <c r="A553" s="26">
+        <v>46317</v>
+      </c>
+      <c r="B553" s="27" t="str">
+        <f t="shared" ref="B553" si="65">TEXT(A553,"aaa")</f>
+        <v>木</v>
+      </c>
+      <c r="C553" s="28" t="s">
+        <v>351</v>
+      </c>
+      <c r="D553" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="E553" s="29">
+        <v>30</v>
+      </c>
+      <c r="F553" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="G553" s="30" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H553" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I553" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J553" s="73" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K553" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="554" spans="1:11">
+      <c r="A554" s="26">
+        <v>46317</v>
+      </c>
+      <c r="B554" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>木</v>
+      </c>
+      <c r="C554" s="28" t="s">
+        <v>712</v>
+      </c>
+      <c r="D554" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E554" s="29">
+        <v>20</v>
+      </c>
+      <c r="F554" s="28" t="s">
+        <v>402</v>
+      </c>
+      <c r="G554" s="30" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H554" s="33">
+        <v>0</v>
+      </c>
+      <c r="I554" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J554" s="73" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K554" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="555" spans="1:11">
+      <c r="A555" s="26">
+        <v>46317</v>
+      </c>
+      <c r="B555" s="27" t="str">
+        <f t="shared" ref="B555" si="66">TEXT(A555,"aaa")</f>
+        <v>木</v>
+      </c>
+      <c r="C555" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="D555" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E555" s="29">
+        <v>50</v>
+      </c>
+      <c r="F555" s="28" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G555" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="H555" s="33">
+        <v>0</v>
+      </c>
+      <c r="I555" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J555" s="73" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K555" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="556" spans="1:11">
+      <c r="A556" s="26">
+        <v>46317</v>
+      </c>
+      <c r="B556" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>木</v>
+      </c>
+      <c r="C556" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D556" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E556" s="29">
+        <v>60</v>
+      </c>
+      <c r="F556" s="28" t="s">
+        <v>970</v>
+      </c>
+      <c r="G556" s="30" t="s">
+        <v>730</v>
+      </c>
+      <c r="H556" s="33">
+        <v>0</v>
+      </c>
+      <c r="I556" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J556" s="73" t="s">
+        <v>1014</v>
+      </c>
+      <c r="K556" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="557" spans="1:11">
+      <c r="A557" s="26">
+        <v>46317</v>
+      </c>
+      <c r="B557" s="27" t="str">
+        <f t="shared" ref="B557" si="67">TEXT(A557,"aaa")</f>
+        <v>木</v>
+      </c>
+      <c r="C557" s="28" t="s">
+        <v>507</v>
+      </c>
+      <c r="D557" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E557" s="29">
+        <v>30</v>
+      </c>
+      <c r="F557" s="28" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G557" s="30" t="s">
+        <v>525</v>
+      </c>
+      <c r="H557" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I557" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J557" s="73" t="s">
+        <v>1016</v>
+      </c>
+      <c r="K557" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="558" spans="1:11">
+      <c r="A558" s="26">
+        <v>46317</v>
+      </c>
+      <c r="B558" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>木</v>
+      </c>
+      <c r="C558" s="38" t="s">
+        <v>925</v>
+      </c>
+      <c r="D558" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="E558" s="39">
+        <v>30</v>
+      </c>
+      <c r="F558" s="40" t="s">
+        <v>565</v>
+      </c>
+      <c r="G558" s="40" t="s">
+        <v>640</v>
+      </c>
+      <c r="H558" s="32">
+        <v>3000</v>
+      </c>
+      <c r="I558" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="J558" s="70" t="s">
+        <v>926</v>
+      </c>
+      <c r="K558" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="559" spans="1:11">
+      <c r="A559" s="26">
+        <v>46318</v>
+      </c>
+      <c r="B559" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>金</v>
+      </c>
+      <c r="C559" s="28" t="s">
+        <v>453</v>
+      </c>
+      <c r="D559" s="28" t="s">
+        <v>935</v>
+      </c>
+      <c r="E559" s="29">
+        <v>20</v>
+      </c>
+      <c r="F559" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G559" s="30" t="s">
+        <v>929</v>
+      </c>
+      <c r="H559" s="33">
+        <v>2500</v>
+      </c>
+      <c r="I559" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J559" s="73" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K559" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="560" spans="1:11">
+      <c r="A560" s="26">
+        <v>46318</v>
+      </c>
+      <c r="B560" s="27" t="str">
+        <f t="shared" ref="B560:B566" si="68">TEXT(A560,"aaa")</f>
+        <v>金</v>
+      </c>
+      <c r="C560" s="28" t="s">
+        <v>676</v>
+      </c>
+      <c r="D560" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E560" s="29">
+        <v>60</v>
+      </c>
+      <c r="F560" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="G560" s="30" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H560" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I560" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J560" s="73" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K560" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="561" spans="1:12">
+      <c r="A561" s="26">
+        <v>46318</v>
+      </c>
+      <c r="B561" s="27" t="str">
+        <f t="shared" si="68"/>
+        <v>金</v>
+      </c>
+      <c r="C561" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D561" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E561" s="29">
+        <v>70</v>
+      </c>
+      <c r="F561" s="28" t="s">
+        <v>970</v>
+      </c>
+      <c r="G561" s="30" t="s">
+        <v>730</v>
+      </c>
+      <c r="H561" s="33">
+        <v>0</v>
+      </c>
+      <c r="I561" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J561" s="73" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K561" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="562" spans="1:12">
+      <c r="A562" s="26">
+        <v>46322</v>
+      </c>
+      <c r="B562" s="27" t="str">
+        <f t="shared" ref="B562" si="69">TEXT(A562,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="C562" s="28" t="s">
+        <v>895</v>
+      </c>
+      <c r="D562" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E562" s="29">
+        <v>60</v>
+      </c>
+      <c r="F562" s="28" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G562" s="30" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H562" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I562" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J562" s="73" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K562" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="563" spans="1:12">
+      <c r="A563" s="26">
+        <v>46322</v>
+      </c>
+      <c r="B563" s="27" t="str">
+        <f t="shared" si="68"/>
+        <v>火</v>
+      </c>
+      <c r="C563" s="28" t="s">
+        <v>627</v>
+      </c>
+      <c r="D563" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="E563" s="29">
+        <v>30</v>
+      </c>
+      <c r="F563" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="G563" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H563" s="33">
+        <v>2000</v>
+      </c>
+      <c r="I563" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J563" s="73" t="s">
+        <v>1023</v>
+      </c>
+      <c r="K563" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="564" spans="1:12">
+      <c r="A564" s="26">
+        <v>46322</v>
+      </c>
+      <c r="B564" s="27" t="str">
+        <f t="shared" ref="B564" si="70">TEXT(A564,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="C564" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="D564" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E564" s="29">
+        <v>40</v>
+      </c>
+      <c r="F564" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="G564" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H564" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I564" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J564" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="K564" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="565" spans="1:12">
+      <c r="A565" s="26">
+        <v>46322</v>
+      </c>
+      <c r="B565" s="27" t="str">
+        <f t="shared" si="68"/>
+        <v>火</v>
+      </c>
+      <c r="C565" s="28" t="s">
+        <v>602</v>
+      </c>
+      <c r="D565" s="28" t="s">
+        <v>935</v>
+      </c>
+      <c r="E565" s="29">
+        <v>20</v>
+      </c>
+      <c r="F565" s="28" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G565" s="30" t="s">
+        <v>929</v>
+      </c>
+      <c r="H565" s="33">
+        <v>2500</v>
+      </c>
+      <c r="I565" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J565" s="73" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K565" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="566" spans="1:12">
+      <c r="A566" s="26">
+        <v>46322</v>
+      </c>
+      <c r="B566" s="27" t="str">
+        <f t="shared" si="68"/>
+        <v>火</v>
+      </c>
+      <c r="C566" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="D566" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="E566" s="29">
+        <v>30</v>
+      </c>
+      <c r="F566" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="G566" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="H566" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I566" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J566" s="73" t="s">
+        <v>987</v>
+      </c>
+      <c r="K566" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="567" spans="1:12">
+      <c r="A567" s="26">
+        <v>46324</v>
+      </c>
+      <c r="B567" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>木</v>
+      </c>
+      <c r="C567" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="D567" s="28" t="s">
+        <v>748</v>
+      </c>
+      <c r="E567" s="29">
+        <v>40</v>
+      </c>
+      <c r="F567" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="G567" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="H567" s="33">
+        <v>3000</v>
+      </c>
+      <c r="I567" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J567" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="K567" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="568" spans="1:12">
+      <c r="A568" s="26">
+        <v>46324</v>
+      </c>
+      <c r="B568" s="27" t="str">
+        <f t="shared" si="56"/>
+        <v>木</v>
+      </c>
+      <c r="C568" s="28" t="s">
+        <v>705</v>
+      </c>
+      <c r="D568" s="28" t="s">
+        <v>706</v>
+      </c>
+      <c r="E568" s="29">
+        <v>30</v>
+      </c>
+      <c r="F568" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G568" s="30" t="s">
+        <v>707</v>
+      </c>
+      <c r="H568" s="31">
+        <v>0</v>
+      </c>
+      <c r="I568" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J568" s="70" t="s">
         <v>927</v>
       </c>
-      <c r="K505" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="L505" s="1" t="s">
+      <c r="K568" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="L568" s="1" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="506" spans="1:12">
-      <c r="A506" s="73"/>
-      <c r="B506" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C506" s="68"/>
-      <c r="D506" s="68"/>
-      <c r="E506" s="69"/>
-      <c r="F506" s="70"/>
-      <c r="G506" s="70"/>
-      <c r="H506" s="71"/>
-      <c r="I506" s="68"/>
-      <c r="J506" s="72"/>
-      <c r="K506" s="1" t="str">
-        <f t="shared" ref="K459:K526" si="46">TEXT(A506,"yyyy-mm-dd")&amp;" "&amp;LEFT(C506,5)&amp;":00"</f>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L506" s="1" t="str">
-        <f t="shared" ref="L459:L526" si="47">" (NULL, '"&amp;K506&amp;"', "&amp;IF(G506="","NULL","'"&amp;G506&amp;"'")&amp;", '"&amp;F506&amp;"', NULL, '"&amp;D506&amp;"', NULL, '"&amp;H506&amp;"', "&amp;IF(E506="","NULL","'"&amp;E506&amp;"'")&amp;", NOW(), NOW()),"</f>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="507" spans="1:12" ht="18.45">
-      <c r="A507" s="44"/>
-      <c r="B507" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C507" s="57"/>
-      <c r="D507" s="57"/>
-      <c r="E507" s="58"/>
-      <c r="F507" s="59"/>
-      <c r="G507" s="59"/>
-      <c r="H507" s="60"/>
-      <c r="I507" s="57"/>
-      <c r="J507" s="61"/>
-      <c r="K507" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L507" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="508" spans="1:12" ht="18.45">
-      <c r="A508" s="44"/>
-      <c r="B508" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C508" s="57"/>
-      <c r="D508" s="57"/>
-      <c r="E508" s="58"/>
-      <c r="F508" s="59"/>
-      <c r="G508" s="59"/>
-      <c r="H508" s="60"/>
-      <c r="I508" s="57"/>
-      <c r="J508" s="61"/>
-      <c r="K508" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L508" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="509" spans="1:12" ht="18.45">
-      <c r="A509" s="44"/>
-      <c r="B509" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C509" s="57"/>
-      <c r="D509" s="57"/>
-      <c r="E509" s="58"/>
-      <c r="F509" s="59"/>
-      <c r="G509" s="59"/>
-      <c r="H509" s="60"/>
-      <c r="I509" s="57"/>
-      <c r="J509" s="61"/>
-      <c r="K509" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L509" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="510" spans="1:12" ht="18.45">
-      <c r="A510" s="44"/>
-      <c r="B510" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C510" s="57"/>
-      <c r="D510" s="57"/>
-      <c r="E510" s="58"/>
-      <c r="F510" s="59"/>
-      <c r="G510" s="59"/>
-      <c r="H510" s="60"/>
-      <c r="I510" s="57"/>
-      <c r="J510" s="61"/>
-      <c r="K510" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L510" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="511" spans="1:12" ht="18.45">
-      <c r="A511" s="44"/>
-      <c r="B511" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C511" s="57"/>
-      <c r="D511" s="57"/>
-      <c r="E511" s="58"/>
-      <c r="F511" s="59"/>
-      <c r="G511" s="59"/>
-      <c r="H511" s="60"/>
-      <c r="I511" s="57"/>
-      <c r="J511" s="61"/>
-      <c r="K511" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L511" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="512" spans="1:12" ht="18.45">
-      <c r="A512" s="44"/>
-      <c r="B512" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C512" s="57"/>
-      <c r="D512" s="57"/>
-      <c r="E512" s="58"/>
-      <c r="F512" s="59"/>
-      <c r="G512" s="59"/>
-      <c r="H512" s="60"/>
-      <c r="I512" s="57"/>
-      <c r="J512" s="61"/>
-      <c r="K512" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L512" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="513" spans="1:12" ht="18.45">
-      <c r="A513" s="44"/>
-      <c r="B513" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C513" s="57"/>
-      <c r="D513" s="57"/>
-      <c r="E513" s="58"/>
-      <c r="F513" s="59"/>
-      <c r="G513" s="59"/>
-      <c r="H513" s="60"/>
-      <c r="I513" s="57"/>
-      <c r="J513" s="61"/>
-      <c r="K513" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L513" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="514" spans="1:12" ht="18.45">
-      <c r="A514" s="44"/>
-      <c r="B514" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C514" s="57"/>
-      <c r="D514" s="57"/>
-      <c r="E514" s="58"/>
-      <c r="F514" s="59"/>
-      <c r="G514" s="59"/>
-      <c r="H514" s="60"/>
-      <c r="I514" s="57"/>
-      <c r="J514" s="61"/>
-      <c r="K514" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L514" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="515" spans="1:12" ht="18.45">
-      <c r="A515" s="44"/>
-      <c r="B515" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C515" s="57"/>
-      <c r="D515" s="57"/>
-      <c r="E515" s="58"/>
-      <c r="F515" s="59"/>
-      <c r="G515" s="59"/>
-      <c r="H515" s="60"/>
-      <c r="I515" s="57"/>
-      <c r="J515" s="61"/>
-      <c r="K515" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L515" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="516" spans="1:12" ht="18.45">
-      <c r="A516" s="44"/>
-      <c r="B516" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C516" s="57"/>
-      <c r="D516" s="57"/>
-      <c r="E516" s="58"/>
-      <c r="F516" s="59"/>
-      <c r="G516" s="59"/>
-      <c r="H516" s="60"/>
-      <c r="I516" s="57"/>
-      <c r="J516" s="61"/>
-      <c r="K516" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L516" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="517" spans="1:12" ht="18.45">
-      <c r="A517" s="44"/>
-      <c r="B517" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C517" s="57"/>
-      <c r="D517" s="57"/>
-      <c r="E517" s="58"/>
-      <c r="F517" s="59"/>
-      <c r="G517" s="59"/>
-      <c r="H517" s="60"/>
-      <c r="I517" s="57"/>
-      <c r="J517" s="61"/>
-      <c r="K517" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L517" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="518" spans="1:12" ht="18.45">
-      <c r="A518" s="44"/>
-      <c r="B518" s="45" t="str">
-        <f t="shared" si="45"/>
-        <v>土</v>
-      </c>
-      <c r="C518" s="57"/>
-      <c r="D518" s="57"/>
-      <c r="E518" s="58"/>
-      <c r="F518" s="59"/>
-      <c r="G518" s="59"/>
-      <c r="H518" s="60"/>
-      <c r="I518" s="57"/>
-      <c r="J518" s="61"/>
-      <c r="K518" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L518" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="519" spans="1:12" ht="18.45">
-      <c r="A519" s="44"/>
-      <c r="B519" s="45" t="str">
-        <f t="shared" ref="B519:B526" si="48">TEXT(A519,"aaa")</f>
-        <v>土</v>
-      </c>
-      <c r="C519" s="57"/>
-      <c r="D519" s="57"/>
-      <c r="E519" s="58"/>
-      <c r="F519" s="59"/>
-      <c r="G519" s="59"/>
-      <c r="H519" s="60"/>
-      <c r="I519" s="57"/>
-      <c r="J519" s="61"/>
-      <c r="K519" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L519" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="520" spans="1:12" ht="18.45">
-      <c r="A520" s="44"/>
-      <c r="B520" s="45" t="str">
-        <f t="shared" si="48"/>
-        <v>土</v>
-      </c>
-      <c r="C520" s="57"/>
-      <c r="D520" s="57"/>
-      <c r="E520" s="58"/>
-      <c r="F520" s="59"/>
-      <c r="G520" s="59"/>
-      <c r="H520" s="60"/>
-      <c r="I520" s="57"/>
-      <c r="J520" s="61"/>
-      <c r="K520" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L520" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="521" spans="1:12" ht="18.45">
-      <c r="A521" s="44"/>
-      <c r="B521" s="45" t="str">
-        <f t="shared" si="48"/>
-        <v>土</v>
-      </c>
-      <c r="C521" s="57"/>
-      <c r="D521" s="57"/>
-      <c r="E521" s="58"/>
-      <c r="F521" s="59"/>
-      <c r="G521" s="59"/>
-      <c r="H521" s="60"/>
-      <c r="I521" s="57"/>
-      <c r="J521" s="61"/>
-      <c r="K521" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L521" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="522" spans="1:12" ht="18.45">
-      <c r="A522" s="44"/>
-      <c r="B522" s="45" t="str">
-        <f t="shared" si="48"/>
-        <v>土</v>
-      </c>
-      <c r="C522" s="57"/>
-      <c r="D522" s="57"/>
-      <c r="E522" s="58"/>
-      <c r="F522" s="59"/>
-      <c r="G522" s="59"/>
-      <c r="H522" s="60"/>
-      <c r="I522" s="57"/>
-      <c r="J522" s="61"/>
-      <c r="K522" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L522" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="523" spans="1:12" ht="18.45">
-      <c r="A523" s="44"/>
-      <c r="B523" s="45" t="str">
-        <f t="shared" si="48"/>
-        <v>土</v>
-      </c>
-      <c r="C523" s="57"/>
-      <c r="D523" s="57"/>
-      <c r="E523" s="58"/>
-      <c r="F523" s="59"/>
-      <c r="G523" s="59"/>
-      <c r="H523" s="60"/>
-      <c r="I523" s="57"/>
-      <c r="J523" s="61"/>
-      <c r="K523" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L523" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="524" spans="1:12" ht="18.45">
-      <c r="A524" s="44"/>
-      <c r="B524" s="45" t="str">
-        <f t="shared" si="48"/>
-        <v>土</v>
-      </c>
-      <c r="C524" s="57"/>
-      <c r="D524" s="57"/>
-      <c r="E524" s="58"/>
-      <c r="F524" s="59"/>
-      <c r="G524" s="59"/>
-      <c r="H524" s="60"/>
-      <c r="I524" s="57"/>
-      <c r="J524" s="61"/>
-      <c r="K524" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L524" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="525" spans="1:12" ht="18.45">
-      <c r="A525" s="44"/>
-      <c r="B525" s="45" t="str">
-        <f t="shared" si="48"/>
-        <v>土</v>
-      </c>
-      <c r="C525" s="57"/>
-      <c r="D525" s="57"/>
-      <c r="E525" s="58"/>
-      <c r="F525" s="59"/>
-      <c r="G525" s="59"/>
-      <c r="H525" s="60"/>
-      <c r="I525" s="57"/>
-      <c r="J525" s="61"/>
-      <c r="K525" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L525" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="526" spans="1:12" ht="18.45">
-      <c r="A526" s="44"/>
-      <c r="B526" s="45" t="str">
-        <f t="shared" si="48"/>
-        <v>土</v>
-      </c>
-      <c r="C526" s="57"/>
-      <c r="D526" s="57"/>
-      <c r="E526" s="58"/>
-      <c r="F526" s="59"/>
-      <c r="G526" s="59"/>
-      <c r="H526" s="60"/>
-      <c r="I526" s="57"/>
-      <c r="J526" s="61"/>
-      <c r="K526" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L526" s="1" t="str">
-        <f t="shared" si="47"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="527" spans="1:12" ht="18.45">
-      <c r="A527" s="44"/>
-      <c r="B527" s="45" t="str">
-        <f t="shared" ref="B527:B577" si="49">TEXT(A527,"aaa")</f>
-        <v>土</v>
-      </c>
-      <c r="C527" s="57"/>
-      <c r="D527" s="57"/>
-      <c r="E527" s="58"/>
-      <c r="F527" s="59"/>
-      <c r="G527" s="59"/>
-      <c r="H527" s="60"/>
-      <c r="I527" s="57"/>
-      <c r="J527" s="61"/>
-      <c r="K527" s="1" t="str">
-        <f t="shared" ref="K458:K577" si="50">TEXT(A527,"yyyy-mm-dd")&amp;" "&amp;LEFT(C527,5)&amp;":00"</f>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L527" s="1" t="str">
-        <f t="shared" ref="L458:L577" si="51">" (NULL, '"&amp;K527&amp;"', "&amp;IF(G527="","NULL","'"&amp;G527&amp;"'")&amp;", '"&amp;F527&amp;"', NULL, '"&amp;D527&amp;"', NULL, '"&amp;H527&amp;"', "&amp;IF(E527="","NULL","'"&amp;E527&amp;"'")&amp;", NOW(), NOW()),"</f>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="528" spans="1:12" ht="18.45">
-      <c r="A528" s="44"/>
-      <c r="B528" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C528" s="57"/>
-      <c r="D528" s="57"/>
-      <c r="E528" s="58"/>
-      <c r="F528" s="59"/>
-      <c r="G528" s="59"/>
-      <c r="H528" s="60"/>
-      <c r="I528" s="57"/>
-      <c r="J528" s="61"/>
-      <c r="K528" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L528" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="529" spans="1:12" ht="18.45">
-      <c r="A529" s="44"/>
-      <c r="B529" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C529" s="57"/>
-      <c r="D529" s="57"/>
-      <c r="E529" s="58"/>
-      <c r="F529" s="59"/>
-      <c r="G529" s="59"/>
-      <c r="H529" s="60"/>
-      <c r="I529" s="57"/>
-      <c r="J529" s="61"/>
-      <c r="K529" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L529" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="530" spans="1:12" ht="18.45">
-      <c r="A530" s="44"/>
-      <c r="B530" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C530" s="57"/>
-      <c r="D530" s="57"/>
-      <c r="E530" s="58"/>
-      <c r="F530" s="59"/>
-      <c r="G530" s="59"/>
-      <c r="H530" s="60"/>
-      <c r="I530" s="57"/>
-      <c r="J530" s="61"/>
-      <c r="K530" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L530" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="531" spans="1:12" ht="18.45">
-      <c r="A531" s="44"/>
-      <c r="B531" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C531" s="57"/>
-      <c r="D531" s="57"/>
-      <c r="E531" s="58"/>
-      <c r="F531" s="59"/>
-      <c r="G531" s="59"/>
-      <c r="H531" s="60"/>
-      <c r="I531" s="57"/>
-      <c r="J531" s="61"/>
-      <c r="K531" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L531" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="532" spans="1:12" ht="18.45">
-      <c r="A532" s="44"/>
-      <c r="B532" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C532" s="57"/>
-      <c r="D532" s="57"/>
-      <c r="E532" s="58"/>
-      <c r="F532" s="59"/>
-      <c r="G532" s="59"/>
-      <c r="H532" s="60"/>
-      <c r="I532" s="57"/>
-      <c r="J532" s="61"/>
-      <c r="K532" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L532" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="533" spans="1:12" ht="18.45">
-      <c r="A533" s="44"/>
-      <c r="B533" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C533" s="57"/>
-      <c r="D533" s="57"/>
-      <c r="E533" s="58"/>
-      <c r="F533" s="59"/>
-      <c r="G533" s="59"/>
-      <c r="H533" s="60"/>
-      <c r="I533" s="57"/>
-      <c r="J533" s="61"/>
-      <c r="K533" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L533" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="534" spans="1:12" ht="18.45">
-      <c r="A534" s="44"/>
-      <c r="B534" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C534" s="57"/>
-      <c r="D534" s="57"/>
-      <c r="E534" s="58"/>
-      <c r="F534" s="59"/>
-      <c r="G534" s="59"/>
-      <c r="H534" s="60"/>
-      <c r="I534" s="57"/>
-      <c r="J534" s="61"/>
-      <c r="K534" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L534" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="535" spans="1:12" ht="18.45">
-      <c r="A535" s="44"/>
-      <c r="B535" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C535" s="57"/>
-      <c r="D535" s="57"/>
-      <c r="E535" s="58"/>
-      <c r="F535" s="59"/>
-      <c r="G535" s="59"/>
-      <c r="H535" s="60"/>
-      <c r="I535" s="57"/>
-      <c r="J535" s="61"/>
-      <c r="K535" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L535" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="536" spans="1:12" ht="18.45">
-      <c r="A536" s="44"/>
-      <c r="B536" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C536" s="57"/>
-      <c r="D536" s="57"/>
-      <c r="E536" s="58"/>
-      <c r="F536" s="59"/>
-      <c r="G536" s="59"/>
-      <c r="H536" s="60"/>
-      <c r="I536" s="57"/>
-      <c r="J536" s="61"/>
-      <c r="K536" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L536" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="537" spans="1:12" ht="18.45">
-      <c r="A537" s="44"/>
-      <c r="B537" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C537" s="57"/>
-      <c r="D537" s="57"/>
-      <c r="E537" s="58"/>
-      <c r="F537" s="59"/>
-      <c r="G537" s="59"/>
-      <c r="H537" s="60"/>
-      <c r="I537" s="57"/>
-      <c r="J537" s="61"/>
-      <c r="K537" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L537" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="538" spans="1:12" ht="18.45">
-      <c r="A538" s="44"/>
-      <c r="B538" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C538" s="57"/>
-      <c r="D538" s="57"/>
-      <c r="E538" s="58"/>
-      <c r="F538" s="59"/>
-      <c r="G538" s="59"/>
-      <c r="H538" s="60"/>
-      <c r="I538" s="57"/>
-      <c r="J538" s="61"/>
-      <c r="K538" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L538" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="539" spans="1:12" ht="18.45">
-      <c r="A539" s="44"/>
-      <c r="B539" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C539" s="57"/>
-      <c r="D539" s="57"/>
-      <c r="E539" s="58"/>
-      <c r="F539" s="59"/>
-      <c r="G539" s="59"/>
-      <c r="H539" s="60"/>
-      <c r="I539" s="57"/>
-      <c r="J539" s="61"/>
-      <c r="K539" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L539" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="540" spans="1:12" ht="18.45">
-      <c r="A540" s="44"/>
-      <c r="B540" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C540" s="57"/>
-      <c r="D540" s="57"/>
-      <c r="E540" s="58"/>
-      <c r="F540" s="59"/>
-      <c r="G540" s="59"/>
-      <c r="H540" s="60"/>
-      <c r="I540" s="57"/>
-      <c r="J540" s="61"/>
-      <c r="K540" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L540" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="541" spans="1:12" ht="18.45">
-      <c r="A541" s="44"/>
-      <c r="B541" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C541" s="57"/>
-      <c r="D541" s="57"/>
-      <c r="E541" s="58"/>
-      <c r="F541" s="59"/>
-      <c r="G541" s="59"/>
-      <c r="H541" s="60"/>
-      <c r="I541" s="57"/>
-      <c r="J541" s="61"/>
-      <c r="K541" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L541" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="542" spans="1:12" ht="18.45">
-      <c r="A542" s="44"/>
-      <c r="B542" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C542" s="57"/>
-      <c r="D542" s="57"/>
-      <c r="E542" s="58"/>
-      <c r="F542" s="59"/>
-      <c r="G542" s="59"/>
-      <c r="H542" s="60"/>
-      <c r="I542" s="57"/>
-      <c r="J542" s="61"/>
-      <c r="K542" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L542" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="543" spans="1:12" ht="18.45">
-      <c r="A543" s="44"/>
-      <c r="B543" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C543" s="57"/>
-      <c r="D543" s="57"/>
-      <c r="E543" s="58"/>
-      <c r="F543" s="59"/>
-      <c r="G543" s="59"/>
-      <c r="H543" s="60"/>
-      <c r="I543" s="57"/>
-      <c r="J543" s="61"/>
-      <c r="K543" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L543" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="544" spans="1:12" ht="18.45">
-      <c r="A544" s="44"/>
-      <c r="B544" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C544" s="57"/>
-      <c r="D544" s="57"/>
-      <c r="E544" s="58"/>
-      <c r="F544" s="59"/>
-      <c r="G544" s="59"/>
-      <c r="H544" s="60"/>
-      <c r="I544" s="57"/>
-      <c r="J544" s="61"/>
-      <c r="K544" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L544" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="545" spans="1:12" ht="18.45">
-      <c r="A545" s="44"/>
-      <c r="B545" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C545" s="57"/>
-      <c r="D545" s="57"/>
-      <c r="E545" s="58"/>
-      <c r="F545" s="59"/>
-      <c r="G545" s="59"/>
-      <c r="H545" s="60"/>
-      <c r="I545" s="57"/>
-      <c r="J545" s="61"/>
-      <c r="K545" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L545" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="546" spans="1:12" ht="18.45">
-      <c r="A546" s="44"/>
-      <c r="B546" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C546" s="57"/>
-      <c r="D546" s="57"/>
-      <c r="E546" s="58"/>
-      <c r="F546" s="59"/>
-      <c r="G546" s="59"/>
-      <c r="H546" s="60"/>
-      <c r="I546" s="57"/>
-      <c r="J546" s="61"/>
-      <c r="K546" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L546" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="547" spans="1:12" ht="18.45">
-      <c r="A547" s="44"/>
-      <c r="B547" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C547" s="57"/>
-      <c r="D547" s="57"/>
-      <c r="E547" s="58"/>
-      <c r="F547" s="59"/>
-      <c r="G547" s="59"/>
-      <c r="H547" s="60"/>
-      <c r="I547" s="57"/>
-      <c r="J547" s="61"/>
-      <c r="K547" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L547" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="548" spans="1:12" ht="18.45">
-      <c r="A548" s="44"/>
-      <c r="B548" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C548" s="57"/>
-      <c r="D548" s="57"/>
-      <c r="E548" s="58"/>
-      <c r="F548" s="59"/>
-      <c r="G548" s="59"/>
-      <c r="H548" s="60"/>
-      <c r="I548" s="57"/>
-      <c r="J548" s="61"/>
-      <c r="K548" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L548" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="549" spans="1:12" ht="18.45">
-      <c r="A549" s="44"/>
-      <c r="B549" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C549" s="57"/>
-      <c r="D549" s="57"/>
-      <c r="E549" s="58"/>
-      <c r="F549" s="59"/>
-      <c r="G549" s="59"/>
-      <c r="H549" s="60"/>
-      <c r="I549" s="57"/>
-      <c r="J549" s="61"/>
-      <c r="K549" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L549" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="550" spans="1:12" ht="18.45">
-      <c r="A550" s="44"/>
-      <c r="B550" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C550" s="57"/>
-      <c r="D550" s="57"/>
-      <c r="E550" s="58"/>
-      <c r="F550" s="59"/>
-      <c r="G550" s="59"/>
-      <c r="H550" s="60"/>
-      <c r="I550" s="57"/>
-      <c r="J550" s="61"/>
-      <c r="K550" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L550" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="551" spans="1:12" ht="18.45">
-      <c r="A551" s="44"/>
-      <c r="B551" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C551" s="57"/>
-      <c r="D551" s="57"/>
-      <c r="E551" s="58"/>
-      <c r="F551" s="59"/>
-      <c r="G551" s="59"/>
-      <c r="H551" s="60"/>
-      <c r="I551" s="57"/>
-      <c r="J551" s="61"/>
-      <c r="K551" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L551" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="552" spans="1:12" ht="18.45">
-      <c r="A552" s="44"/>
-      <c r="B552" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C552" s="57"/>
-      <c r="D552" s="57"/>
-      <c r="E552" s="58"/>
-      <c r="F552" s="59"/>
-      <c r="G552" s="59"/>
-      <c r="H552" s="60"/>
-      <c r="I552" s="57"/>
-      <c r="J552" s="61"/>
-      <c r="K552" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L552" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="553" spans="1:12" ht="18.45">
-      <c r="A553" s="44"/>
-      <c r="B553" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C553" s="57"/>
-      <c r="D553" s="57"/>
-      <c r="E553" s="58"/>
-      <c r="F553" s="59"/>
-      <c r="G553" s="59"/>
-      <c r="H553" s="60"/>
-      <c r="I553" s="57"/>
-      <c r="J553" s="61"/>
-      <c r="K553" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L553" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="554" spans="1:12" ht="18.45">
-      <c r="A554" s="44"/>
-      <c r="B554" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C554" s="57"/>
-      <c r="D554" s="57"/>
-      <c r="E554" s="58"/>
-      <c r="F554" s="59"/>
-      <c r="G554" s="59"/>
-      <c r="H554" s="60"/>
-      <c r="I554" s="57"/>
-      <c r="J554" s="61"/>
-      <c r="K554" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L554" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="555" spans="1:12" ht="18.45">
-      <c r="A555" s="44"/>
-      <c r="B555" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C555" s="57"/>
-      <c r="D555" s="57"/>
-      <c r="E555" s="58"/>
-      <c r="F555" s="59"/>
-      <c r="G555" s="59"/>
-      <c r="H555" s="60"/>
-      <c r="I555" s="57"/>
-      <c r="J555" s="61"/>
-      <c r="K555" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L555" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="556" spans="1:12" ht="18.45">
-      <c r="A556" s="44"/>
-      <c r="B556" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C556" s="57"/>
-      <c r="D556" s="57"/>
-      <c r="E556" s="58"/>
-      <c r="F556" s="59"/>
-      <c r="G556" s="59"/>
-      <c r="H556" s="60"/>
-      <c r="I556" s="57"/>
-      <c r="J556" s="61"/>
-      <c r="K556" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L556" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="557" spans="1:12" ht="18.45">
-      <c r="A557" s="44"/>
-      <c r="B557" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C557" s="57"/>
-      <c r="D557" s="57"/>
-      <c r="E557" s="58"/>
-      <c r="F557" s="59"/>
-      <c r="G557" s="59"/>
-      <c r="H557" s="60"/>
-      <c r="I557" s="57"/>
-      <c r="J557" s="61"/>
-      <c r="K557" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L557" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="558" spans="1:12" ht="18.45">
-      <c r="A558" s="44"/>
-      <c r="B558" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C558" s="57"/>
-      <c r="D558" s="57"/>
-      <c r="E558" s="58"/>
-      <c r="F558" s="59"/>
-      <c r="G558" s="59"/>
-      <c r="H558" s="60"/>
-      <c r="I558" s="57"/>
-      <c r="J558" s="61"/>
-      <c r="K558" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L558" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="559" spans="1:12" ht="18.45">
-      <c r="A559" s="44"/>
-      <c r="B559" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C559" s="57"/>
-      <c r="D559" s="57"/>
-      <c r="E559" s="58"/>
-      <c r="F559" s="59"/>
-      <c r="G559" s="59"/>
-      <c r="H559" s="60"/>
-      <c r="I559" s="57"/>
-      <c r="J559" s="61"/>
-      <c r="K559" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L559" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="560" spans="1:12" ht="18.45">
-      <c r="A560" s="44"/>
-      <c r="B560" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C560" s="57"/>
-      <c r="D560" s="57"/>
-      <c r="E560" s="58"/>
-      <c r="F560" s="59"/>
-      <c r="G560" s="59"/>
-      <c r="H560" s="60"/>
-      <c r="I560" s="57"/>
-      <c r="J560" s="61"/>
-      <c r="K560" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L560" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="561" spans="1:12" ht="18.45">
-      <c r="A561" s="44"/>
-      <c r="B561" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C561" s="57"/>
-      <c r="D561" s="57"/>
-      <c r="E561" s="58"/>
-      <c r="F561" s="59"/>
-      <c r="G561" s="59"/>
-      <c r="H561" s="60"/>
-      <c r="I561" s="57"/>
-      <c r="J561" s="61"/>
-      <c r="K561" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L561" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="562" spans="1:12" ht="18.45">
-      <c r="A562" s="44"/>
-      <c r="B562" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C562" s="57"/>
-      <c r="D562" s="57"/>
-      <c r="E562" s="58"/>
-      <c r="F562" s="59"/>
-      <c r="G562" s="59"/>
-      <c r="H562" s="60"/>
-      <c r="I562" s="57"/>
-      <c r="J562" s="61"/>
-      <c r="K562" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L562" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="563" spans="1:12" ht="18.45">
-      <c r="A563" s="44"/>
-      <c r="B563" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C563" s="57"/>
-      <c r="D563" s="57"/>
-      <c r="E563" s="58"/>
-      <c r="F563" s="59"/>
-      <c r="G563" s="59"/>
-      <c r="H563" s="60"/>
-      <c r="I563" s="57"/>
-      <c r="J563" s="61"/>
-      <c r="K563" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L563" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="564" spans="1:12" ht="18.45">
-      <c r="A564" s="44"/>
-      <c r="B564" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C564" s="57"/>
-      <c r="D564" s="57"/>
-      <c r="E564" s="58"/>
-      <c r="F564" s="59"/>
-      <c r="G564" s="59"/>
-      <c r="H564" s="60"/>
-      <c r="I564" s="57"/>
-      <c r="J564" s="61"/>
-      <c r="K564" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L564" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="565" spans="1:12" ht="18.45">
-      <c r="A565" s="44"/>
-      <c r="B565" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C565" s="57"/>
-      <c r="D565" s="57"/>
-      <c r="E565" s="58"/>
-      <c r="F565" s="59"/>
-      <c r="G565" s="59"/>
-      <c r="H565" s="60"/>
-      <c r="I565" s="57"/>
-      <c r="J565" s="61"/>
-      <c r="K565" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L565" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="566" spans="1:12" ht="18.45">
-      <c r="A566" s="44"/>
-      <c r="B566" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C566" s="57"/>
-      <c r="D566" s="57"/>
-      <c r="E566" s="58"/>
-      <c r="F566" s="59"/>
-      <c r="G566" s="59"/>
-      <c r="H566" s="60"/>
-      <c r="I566" s="57"/>
-      <c r="J566" s="61"/>
-      <c r="K566" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L566" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="567" spans="1:12" ht="18.45">
-      <c r="A567" s="44"/>
-      <c r="B567" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C567" s="57"/>
-      <c r="D567" s="57"/>
-      <c r="E567" s="58"/>
-      <c r="F567" s="59"/>
-      <c r="G567" s="59"/>
-      <c r="H567" s="60"/>
-      <c r="I567" s="57"/>
-      <c r="J567" s="61"/>
-      <c r="K567" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L567" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="568" spans="1:12" ht="18.45">
-      <c r="A568" s="44"/>
-      <c r="B568" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C568" s="57"/>
-      <c r="D568" s="57"/>
-      <c r="E568" s="58"/>
-      <c r="F568" s="59"/>
-      <c r="G568" s="59"/>
-      <c r="H568" s="60"/>
-      <c r="I568" s="57"/>
-      <c r="J568" s="61"/>
-      <c r="K568" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
-      </c>
-      <c r="L568" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
-      </c>
-    </row>
-    <row r="569" spans="1:12" ht="18.45">
-      <c r="A569" s="44"/>
+    <row r="569" spans="1:12">
+      <c r="A569" s="44">
+        <v>46331</v>
+      </c>
       <c r="B569" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
-      </c>
-      <c r="C569" s="57"/>
-      <c r="D569" s="57"/>
-      <c r="E569" s="58"/>
-      <c r="F569" s="59"/>
-      <c r="G569" s="59"/>
-      <c r="H569" s="60"/>
-      <c r="I569" s="57"/>
-      <c r="J569" s="61"/>
+        <f t="shared" si="56"/>
+        <v>木</v>
+      </c>
+      <c r="C569" s="66" t="s">
+        <v>627</v>
+      </c>
+      <c r="D569" s="66" t="s">
+        <v>446</v>
+      </c>
+      <c r="E569" s="67">
+        <v>50</v>
+      </c>
+      <c r="F569" s="68" t="s">
+        <v>447</v>
+      </c>
+      <c r="G569" s="68" t="s">
+        <v>48</v>
+      </c>
+      <c r="H569" s="77">
+        <v>3000</v>
+      </c>
+      <c r="I569" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="J569" s="69" t="s">
+        <v>1027</v>
+      </c>
       <c r="K569" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
+        <f t="shared" ref="K569:K589" si="71">TEXT(A569,"yyyy-mm-dd")&amp;" "&amp;LEFT(C569,5)&amp;":00"</f>
+        <v>2026-11-05 16:00:00</v>
       </c>
       <c r="L569" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+        <f t="shared" ref="L569:L589" si="72">" (NULL, '"&amp;K569&amp;"', "&amp;IF(G569="","NULL","'"&amp;G569&amp;"'")&amp;", '"&amp;F569&amp;"', NULL, '"&amp;D569&amp;"', NULL, '"&amp;H569&amp;"', "&amp;IF(E569="","NULL","'"&amp;E569&amp;"'")&amp;", NOW(), NOW()),"</f>
+        <v xml:space="preserve"> (NULL, '2026-11-05 16:00:00', 'zetto', 'SES交流会 ', NULL, '新宿', NULL, '3000', '50', NOW(), NOW()),</v>
       </c>
     </row>
     <row r="570" spans="1:12" ht="18.45">
-      <c r="A570" s="44"/>
+      <c r="A570" s="44">
+        <v>46332</v>
+      </c>
       <c r="B570" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
+        <f t="shared" si="56"/>
+        <v>金</v>
       </c>
       <c r="C570" s="57"/>
       <c r="D570" s="57"/>
@@ -23350,18 +24586,20 @@
       <c r="I570" s="57"/>
       <c r="J570" s="61"/>
       <c r="K570" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
+        <f t="shared" si="71"/>
+        <v>2026-11-06 :00</v>
       </c>
       <c r="L570" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-06 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
       </c>
     </row>
     <row r="571" spans="1:12" ht="18.45">
-      <c r="A571" s="44"/>
+      <c r="A571" s="44">
+        <v>46333</v>
+      </c>
       <c r="B571" s="45" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="56"/>
         <v>土</v>
       </c>
       <c r="C571" s="57"/>
@@ -23373,19 +24611,21 @@
       <c r="I571" s="57"/>
       <c r="J571" s="61"/>
       <c r="K571" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
+        <f t="shared" si="71"/>
+        <v>2026-11-07 :00</v>
       </c>
       <c r="L571" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-07 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
       </c>
     </row>
     <row r="572" spans="1:12" ht="18.45">
-      <c r="A572" s="44"/>
+      <c r="A572" s="44">
+        <v>46334</v>
+      </c>
       <c r="B572" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
+        <f t="shared" si="56"/>
+        <v>日</v>
       </c>
       <c r="C572" s="57"/>
       <c r="D572" s="57"/>
@@ -23396,19 +24636,21 @@
       <c r="I572" s="57"/>
       <c r="J572" s="61"/>
       <c r="K572" s="1" t="str">
-        <f t="shared" si="50"/>
-        <v>1900-01-00 :00</v>
+        <f t="shared" si="71"/>
+        <v>2026-11-08 :00</v>
       </c>
       <c r="L572" s="1" t="str">
-        <f t="shared" si="51"/>
-        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-08 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
       </c>
     </row>
     <row r="573" spans="1:12" ht="18.45">
-      <c r="A573" s="44"/>
+      <c r="A573" s="44">
+        <v>46335</v>
+      </c>
       <c r="B573" s="45" t="str">
-        <f t="shared" si="49"/>
-        <v>土</v>
+        <f t="shared" si="56"/>
+        <v>月</v>
       </c>
       <c r="C573" s="57"/>
       <c r="D573" s="57"/>
@@ -23419,145 +24661,1840 @@
       <c r="I573" s="57"/>
       <c r="J573" s="61"/>
       <c r="K573" s="1" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="71"/>
+        <v>2026-11-09 :00</v>
+      </c>
+      <c r="L573" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-09 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="574" spans="1:12" ht="18.45">
+      <c r="A574" s="44">
+        <v>46336</v>
+      </c>
+      <c r="B574" s="45" t="str">
+        <f t="shared" si="56"/>
+        <v>火</v>
+      </c>
+      <c r="C574" s="57" t="s">
+        <v>648</v>
+      </c>
+      <c r="D574" s="57" t="s">
+        <v>446</v>
+      </c>
+      <c r="E574" s="58">
+        <v>300</v>
+      </c>
+      <c r="F574" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G574" s="59" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H574" s="60">
+        <v>2000</v>
+      </c>
+      <c r="I574" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J574" s="61" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K574" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-10 17:45:00</v>
+      </c>
+      <c r="L574" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-10 17:45:00', '株式会社LEGAREA', 'SES交流会', NULL, '新宿', NULL, '2000', '300', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="575" spans="1:12" ht="18.45">
+      <c r="A575" s="44">
+        <v>46337</v>
+      </c>
+      <c r="B575" s="45" t="str">
+        <f t="shared" si="56"/>
+        <v>水</v>
+      </c>
+      <c r="C575" s="57" t="s">
+        <v>490</v>
+      </c>
+      <c r="D575" s="57" t="s">
+        <v>241</v>
+      </c>
+      <c r="E575" s="58">
+        <v>200</v>
+      </c>
+      <c r="F575" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="G575" s="59" t="s">
+        <v>260</v>
+      </c>
+      <c r="H575" s="60">
+        <v>0</v>
+      </c>
+      <c r="I575" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J575" s="61" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K575" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-11 14:00:00</v>
+      </c>
+      <c r="L575" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-11 14:00:00', '株式会社KOKORO', 'SES/IT業界向け情報交換会', NULL, '蒲田', NULL, '0', '200', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="576" spans="1:12" ht="18.45">
+      <c r="A576" s="44">
+        <v>46337</v>
+      </c>
+      <c r="B576" s="45" t="str">
+        <f t="shared" si="56"/>
+        <v>水</v>
+      </c>
+      <c r="C576" s="57" t="s">
+        <v>396</v>
+      </c>
+      <c r="D576" s="57" t="s">
+        <v>251</v>
+      </c>
+      <c r="E576" s="58">
+        <v>30</v>
+      </c>
+      <c r="F576" s="59" t="s">
+        <v>634</v>
+      </c>
+      <c r="G576" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="H576" s="60">
+        <v>3000</v>
+      </c>
+      <c r="I576" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="J576" s="61" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K576" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-11 19:00:00</v>
+      </c>
+      <c r="L576" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-11 19:00:00', 'zetto', 'SES×BUSINESS×フットサル交流会', NULL, '東陽町', NULL, '3000', '30', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="577" spans="1:12" ht="18.45">
+      <c r="A577" s="44">
+        <v>46338</v>
+      </c>
+      <c r="B577" s="45" t="str">
+        <f t="shared" si="56"/>
+        <v>木</v>
+      </c>
+      <c r="C577" s="57" t="s">
+        <v>785</v>
+      </c>
+      <c r="D577" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="E577" s="58">
+        <v>120</v>
+      </c>
+      <c r="F577" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="G577" s="59"/>
+      <c r="H577" s="60">
+        <v>2000</v>
+      </c>
+      <c r="I577" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J577" s="61" t="s">
+        <v>1032</v>
+      </c>
+      <c r="K577" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-12 14:30:00</v>
+      </c>
+      <c r="L577" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-12 14:30:00', NULL, 'SES/IT業界向け 情報交換会', NULL, '池袋', NULL, '2000', '120', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="578" spans="1:12" ht="18.45">
+      <c r="A578" s="44">
+        <v>46338</v>
+      </c>
+      <c r="B578" s="45" t="str">
+        <f t="shared" si="56"/>
+        <v>木</v>
+      </c>
+      <c r="C578" s="57" t="s">
+        <v>627</v>
+      </c>
+      <c r="D578" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="E578" s="58">
+        <v>30</v>
+      </c>
+      <c r="F578" s="59" t="s">
+        <v>465</v>
+      </c>
+      <c r="G578" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="H578" s="78">
+        <v>3000</v>
+      </c>
+      <c r="I578" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="J578" s="61" t="s">
+        <v>1033</v>
+      </c>
+      <c r="K578" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-12 16:00:00</v>
+      </c>
+      <c r="L578" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-12 16:00:00', 'zetto', 'SES/IT交流会 ', NULL, '横浜', NULL, '3000', '30', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="579" spans="1:12" ht="18.45">
+      <c r="A579" s="44">
+        <v>46339</v>
+      </c>
+      <c r="B579" s="45" t="str">
+        <f t="shared" si="56"/>
+        <v>金</v>
+      </c>
+      <c r="C579" s="57"/>
+      <c r="D579" s="57"/>
+      <c r="E579" s="58"/>
+      <c r="F579" s="59"/>
+      <c r="G579" s="59"/>
+      <c r="H579" s="60"/>
+      <c r="I579" s="57"/>
+      <c r="J579" s="61"/>
+      <c r="K579" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-13 :00</v>
+      </c>
+      <c r="L579" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-13 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="580" spans="1:12" ht="18.45">
+      <c r="A580" s="44">
+        <v>46340</v>
+      </c>
+      <c r="B580" s="45" t="str">
+        <f t="shared" si="56"/>
+        <v>土</v>
+      </c>
+      <c r="C580" s="57"/>
+      <c r="D580" s="57"/>
+      <c r="E580" s="58"/>
+      <c r="F580" s="59"/>
+      <c r="G580" s="59"/>
+      <c r="H580" s="60"/>
+      <c r="I580" s="57"/>
+      <c r="J580" s="61"/>
+      <c r="K580" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-14 :00</v>
+      </c>
+      <c r="L580" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-14 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="581" spans="1:12" ht="18.45">
+      <c r="A581" s="44">
+        <v>46341</v>
+      </c>
+      <c r="B581" s="45" t="str">
+        <f t="shared" si="56"/>
+        <v>日</v>
+      </c>
+      <c r="C581" s="57"/>
+      <c r="D581" s="57"/>
+      <c r="E581" s="58"/>
+      <c r="F581" s="59"/>
+      <c r="G581" s="59"/>
+      <c r="H581" s="60"/>
+      <c r="I581" s="57"/>
+      <c r="J581" s="61"/>
+      <c r="K581" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-15 :00</v>
+      </c>
+      <c r="L581" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-15 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="582" spans="1:12" ht="18.45">
+      <c r="A582" s="44">
+        <v>46342</v>
+      </c>
+      <c r="B582" s="45" t="str">
+        <f t="shared" ref="B582:B589" si="73">TEXT(A582,"aaa")</f>
+        <v>月</v>
+      </c>
+      <c r="C582" s="57"/>
+      <c r="D582" s="57"/>
+      <c r="E582" s="58"/>
+      <c r="F582" s="59"/>
+      <c r="G582" s="59"/>
+      <c r="H582" s="60"/>
+      <c r="I582" s="57"/>
+      <c r="J582" s="61"/>
+      <c r="K582" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-16 :00</v>
+      </c>
+      <c r="L582" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-16 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="583" spans="1:12" ht="18.45">
+      <c r="A583" s="44">
+        <v>46343</v>
+      </c>
+      <c r="B583" s="45" t="str">
+        <f t="shared" si="73"/>
+        <v>火</v>
+      </c>
+      <c r="C583" s="57"/>
+      <c r="D583" s="57"/>
+      <c r="E583" s="58"/>
+      <c r="F583" s="59"/>
+      <c r="G583" s="59"/>
+      <c r="H583" s="60"/>
+      <c r="I583" s="57"/>
+      <c r="J583" s="61"/>
+      <c r="K583" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-17 :00</v>
+      </c>
+      <c r="L583" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-17 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="584" spans="1:12" ht="18.45">
+      <c r="A584" s="44">
+        <v>46344</v>
+      </c>
+      <c r="B584" s="45" t="str">
+        <f t="shared" si="73"/>
+        <v>水</v>
+      </c>
+      <c r="C584" s="57" t="s">
+        <v>412</v>
+      </c>
+      <c r="D584" s="57" t="s">
+        <v>558</v>
+      </c>
+      <c r="E584" s="58"/>
+      <c r="F584" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="G584" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="H584" s="60">
+        <v>0</v>
+      </c>
+      <c r="I584" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="J584" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="K584" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-18 18:50:00</v>
+      </c>
+      <c r="L584" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-18 18:50:00', '株式会社ベルナー', 'ITビジネス交流会', NULL, '名古屋', NULL, '0', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="585" spans="1:12" ht="18.45">
+      <c r="A585" s="44">
+        <v>46345</v>
+      </c>
+      <c r="B585" s="45" t="str">
+        <f t="shared" si="73"/>
+        <v>木</v>
+      </c>
+      <c r="C585" s="57" t="s">
+        <v>412</v>
+      </c>
+      <c r="D585" s="57" t="s">
+        <v>354</v>
+      </c>
+      <c r="E585" s="58"/>
+      <c r="F585" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="G585" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="H585" s="60">
+        <v>0</v>
+      </c>
+      <c r="I585" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="J585" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="K585" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-19 18:50:00</v>
+      </c>
+      <c r="L585" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-19 18:50:00', '株式会社ベルナー', 'ITビジネス交流会', NULL, '新橋', NULL, '0', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="586" spans="1:12" ht="18.45">
+      <c r="A586" s="44">
+        <v>46346</v>
+      </c>
+      <c r="B586" s="45" t="str">
+        <f t="shared" si="73"/>
+        <v>金</v>
+      </c>
+      <c r="C586" s="57" t="s">
+        <v>656</v>
+      </c>
+      <c r="D586" s="57" t="s">
+        <v>469</v>
+      </c>
+      <c r="E586" s="58">
+        <v>20</v>
+      </c>
+      <c r="F586" s="59" t="s">
+        <v>465</v>
+      </c>
+      <c r="G586" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="H586" s="60">
+        <v>3000</v>
+      </c>
+      <c r="I586" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J586" s="61" t="s">
+        <v>1034</v>
+      </c>
+      <c r="K586" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-20 18:30:00</v>
+      </c>
+      <c r="L586" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-20 18:30:00', 'zetto', 'SES/IT交流会 ', NULL, '札幌', NULL, '3000', '20', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="587" spans="1:12" ht="18.45">
+      <c r="A587" s="44">
+        <v>46347</v>
+      </c>
+      <c r="B587" s="45" t="str">
+        <f t="shared" si="73"/>
+        <v>土</v>
+      </c>
+      <c r="C587" s="57"/>
+      <c r="D587" s="57"/>
+      <c r="E587" s="58"/>
+      <c r="F587" s="59"/>
+      <c r="G587" s="59"/>
+      <c r="H587" s="60"/>
+      <c r="I587" s="57"/>
+      <c r="J587" s="61"/>
+      <c r="K587" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-21 :00</v>
+      </c>
+      <c r="L587" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-21 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="588" spans="1:12" ht="18.45">
+      <c r="A588" s="44">
+        <v>46348</v>
+      </c>
+      <c r="B588" s="45" t="str">
+        <f t="shared" si="73"/>
+        <v>日</v>
+      </c>
+      <c r="C588" s="57"/>
+      <c r="D588" s="57"/>
+      <c r="E588" s="58"/>
+      <c r="F588" s="59"/>
+      <c r="G588" s="59"/>
+      <c r="H588" s="60"/>
+      <c r="I588" s="57"/>
+      <c r="J588" s="61"/>
+      <c r="K588" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-22 :00</v>
+      </c>
+      <c r="L588" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-22 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="589" spans="1:12" ht="18.45">
+      <c r="A589" s="44">
+        <v>46349</v>
+      </c>
+      <c r="B589" s="45" t="str">
+        <f t="shared" si="73"/>
+        <v>月</v>
+      </c>
+      <c r="C589" s="57"/>
+      <c r="D589" s="57"/>
+      <c r="E589" s="58"/>
+      <c r="F589" s="59"/>
+      <c r="G589" s="59"/>
+      <c r="H589" s="60"/>
+      <c r="I589" s="57"/>
+      <c r="J589" s="61"/>
+      <c r="K589" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>2026-11-23 :00</v>
+      </c>
+      <c r="L589" s="1" t="str">
+        <f t="shared" si="72"/>
+        <v xml:space="preserve"> (NULL, '2026-11-23 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="590" spans="1:12" ht="18.45">
+      <c r="A590" s="44">
+        <v>46350</v>
+      </c>
+      <c r="B590" s="45" t="str">
+        <f t="shared" ref="B590:B640" si="74">TEXT(A590,"aaa")</f>
+        <v>火</v>
+      </c>
+      <c r="C590" s="57" t="s">
+        <v>396</v>
+      </c>
+      <c r="D590" s="57" t="s">
+        <v>428</v>
+      </c>
+      <c r="E590" s="58">
+        <v>120</v>
+      </c>
+      <c r="F590" s="59" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G590" s="59" t="s">
+        <v>429</v>
+      </c>
+      <c r="H590" s="60">
+        <v>5000</v>
+      </c>
+      <c r="I590" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J590" s="61" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K590" s="1" t="str">
+        <f t="shared" ref="K590:K640" si="75">TEXT(A590,"yyyy-mm-dd")&amp;" "&amp;LEFT(C590,5)&amp;":00"</f>
+        <v>2026-11-24 19:00:00</v>
+      </c>
+      <c r="L590" s="1" t="str">
+        <f t="shared" ref="L590:L640" si="76">" (NULL, '"&amp;K590&amp;"', "&amp;IF(G590="","NULL","'"&amp;G590&amp;"'")&amp;", '"&amp;F590&amp;"', NULL, '"&amp;D590&amp;"', NULL, '"&amp;H590&amp;"', "&amp;IF(E590="","NULL","'"&amp;E590&amp;"'")&amp;", NOW(), NOW()),"</f>
+        <v xml:space="preserve"> (NULL, '2026-11-24 19:00:00', '株式会社シー・エス・エス', '少し早めのIT企業忘年会', NULL, '五反田', NULL, '5000', '120', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="591" spans="1:12" ht="18.45">
+      <c r="A591" s="44">
+        <v>46351</v>
+      </c>
+      <c r="B591" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>水</v>
+      </c>
+      <c r="C591" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="D591" s="57" t="s">
+        <v>558</v>
+      </c>
+      <c r="E591" s="58">
+        <v>50</v>
+      </c>
+      <c r="F591" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G591" s="59" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H591" s="60">
+        <v>0</v>
+      </c>
+      <c r="I591" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J591" s="61" t="s">
+        <v>1038</v>
+      </c>
+      <c r="K591" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>2026-11-25 16:00:00</v>
+      </c>
+      <c r="L591" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '2026-11-25 16:00:00', '株式会社セラク', 'SES交流会', NULL, '名古屋', NULL, '0', '50', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="592" spans="1:12" ht="18.45">
+      <c r="A592" s="44">
+        <v>46351</v>
+      </c>
+      <c r="B592" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>水</v>
+      </c>
+      <c r="C592" s="57" t="s">
+        <v>627</v>
+      </c>
+      <c r="D592" s="57" t="s">
+        <v>748</v>
+      </c>
+      <c r="E592" s="58">
+        <v>70</v>
+      </c>
+      <c r="F592" s="59" t="s">
+        <v>447</v>
+      </c>
+      <c r="G592" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="H592" s="78">
+        <v>3000</v>
+      </c>
+      <c r="I592" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="J592" s="61" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K592" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>2026-11-25 16:00:00</v>
+      </c>
+      <c r="L592" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '2026-11-25 16:00:00', 'zetto', 'SES交流会 ', NULL, '秋葉原', NULL, '3000', '70', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="593" spans="1:12" ht="18.45">
+      <c r="A593" s="44">
+        <v>46352</v>
+      </c>
+      <c r="B593" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>木</v>
+      </c>
+      <c r="C593" s="57" t="s">
+        <v>627</v>
+      </c>
+      <c r="D593" s="57" t="s">
+        <v>558</v>
+      </c>
+      <c r="E593" s="58">
+        <v>30</v>
+      </c>
+      <c r="F593" s="59" t="s">
+        <v>465</v>
+      </c>
+      <c r="G593" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="H593" s="78">
+        <v>3000</v>
+      </c>
+      <c r="I593" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="J593" s="61" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K593" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>2026-11-26 16:00:00</v>
+      </c>
+      <c r="L593" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '2026-11-26 16:00:00', 'zetto', 'SES/IT交流会 ', NULL, '名古屋', NULL, '3000', '30', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="594" spans="1:12" ht="18.45">
+      <c r="A594" s="44">
+        <v>46352</v>
+      </c>
+      <c r="B594" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>木</v>
+      </c>
+      <c r="C594" s="57" t="s">
+        <v>366</v>
+      </c>
+      <c r="D594" s="57" t="s">
+        <v>748</v>
+      </c>
+      <c r="E594" s="58">
+        <v>40</v>
+      </c>
+      <c r="F594" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="G594" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="H594" s="60">
+        <v>3000</v>
+      </c>
+      <c r="I594" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="J594" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="K594" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>2026-11-26 17:00:00</v>
+      </c>
+      <c r="L594" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '2026-11-26 17:00:00', 'microsyz', 'SES交流会', NULL, '秋葉原', NULL, '3000', '40', NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="595" spans="1:12" ht="18.45">
+      <c r="A595" s="44">
+        <v>46353</v>
+      </c>
+      <c r="B595" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>金</v>
+      </c>
+      <c r="C595" s="57"/>
+      <c r="D595" s="57"/>
+      <c r="E595" s="58"/>
+      <c r="F595" s="59"/>
+      <c r="G595" s="59"/>
+      <c r="H595" s="60"/>
+      <c r="I595" s="57"/>
+      <c r="J595" s="61"/>
+      <c r="K595" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>2026-11-27 :00</v>
+      </c>
+      <c r="L595" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '2026-11-27 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="596" spans="1:12" ht="18.45">
+      <c r="A596" s="44"/>
+      <c r="B596" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C596" s="57"/>
+      <c r="D596" s="57"/>
+      <c r="E596" s="58"/>
+      <c r="F596" s="59"/>
+      <c r="G596" s="59"/>
+      <c r="H596" s="60"/>
+      <c r="I596" s="57"/>
+      <c r="J596" s="61"/>
+      <c r="K596" s="1" t="str">
+        <f t="shared" si="75"/>
         <v>1900-01-00 :00</v>
       </c>
-      <c r="L573" s="1" t="str">
-        <f t="shared" si="51"/>
+      <c r="L596" s="1" t="str">
+        <f t="shared" si="76"/>
         <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
       </c>
     </row>
-    <row r="574" spans="1:12" ht="18.45">
-      <c r="A574" s="44"/>
-      <c r="B574" s="45" t="str">
-        <f t="shared" si="49"/>
+    <row r="597" spans="1:12" ht="18.45">
+      <c r="A597" s="44"/>
+      <c r="B597" s="45" t="str">
+        <f t="shared" si="74"/>
         <v>土</v>
       </c>
-      <c r="C574" s="57"/>
-      <c r="D574" s="57"/>
-      <c r="E574" s="58"/>
-      <c r="F574" s="59"/>
-      <c r="G574" s="59"/>
-      <c r="H574" s="60"/>
-      <c r="I574" s="57"/>
-      <c r="J574" s="61"/>
-      <c r="K574" s="1" t="str">
-        <f t="shared" si="50"/>
+      <c r="C597" s="57"/>
+      <c r="D597" s="57"/>
+      <c r="E597" s="58"/>
+      <c r="F597" s="59"/>
+      <c r="G597" s="59"/>
+      <c r="H597" s="60"/>
+      <c r="I597" s="57"/>
+      <c r="J597" s="61"/>
+      <c r="K597" s="1" t="str">
+        <f t="shared" si="75"/>
         <v>1900-01-00 :00</v>
       </c>
-      <c r="L574" s="1" t="str">
-        <f t="shared" si="51"/>
+      <c r="L597" s="1" t="str">
+        <f t="shared" si="76"/>
         <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
       </c>
     </row>
-    <row r="575" spans="1:12" ht="18.45">
-      <c r="A575" s="44"/>
-      <c r="B575" s="45" t="str">
-        <f t="shared" si="49"/>
+    <row r="598" spans="1:12" ht="18.45">
+      <c r="A598" s="44"/>
+      <c r="B598" s="45" t="str">
+        <f t="shared" si="74"/>
         <v>土</v>
       </c>
-      <c r="C575" s="57"/>
-      <c r="D575" s="57"/>
-      <c r="E575" s="58"/>
-      <c r="F575" s="59"/>
-      <c r="G575" s="59"/>
-      <c r="H575" s="60"/>
-      <c r="I575" s="57"/>
-      <c r="J575" s="61"/>
-      <c r="K575" s="1" t="str">
-        <f t="shared" si="50"/>
+      <c r="C598" s="57"/>
+      <c r="D598" s="57"/>
+      <c r="E598" s="58"/>
+      <c r="F598" s="59"/>
+      <c r="G598" s="59"/>
+      <c r="H598" s="60"/>
+      <c r="I598" s="57"/>
+      <c r="J598" s="61"/>
+      <c r="K598" s="1" t="str">
+        <f t="shared" si="75"/>
         <v>1900-01-00 :00</v>
       </c>
-      <c r="L575" s="1" t="str">
-        <f t="shared" si="51"/>
+      <c r="L598" s="1" t="str">
+        <f t="shared" si="76"/>
         <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
       </c>
     </row>
-    <row r="576" spans="1:12" ht="18.45">
-      <c r="A576" s="44"/>
-      <c r="B576" s="45" t="str">
-        <f t="shared" si="49"/>
+    <row r="599" spans="1:12" ht="18.45">
+      <c r="A599" s="44"/>
+      <c r="B599" s="45" t="str">
+        <f t="shared" si="74"/>
         <v>土</v>
       </c>
-      <c r="C576" s="57"/>
-      <c r="D576" s="57"/>
-      <c r="E576" s="58"/>
-      <c r="F576" s="59"/>
-      <c r="G576" s="59"/>
-      <c r="H576" s="60"/>
-      <c r="I576" s="57"/>
-      <c r="J576" s="61"/>
-      <c r="K576" s="1" t="str">
-        <f t="shared" si="50"/>
+      <c r="C599" s="57"/>
+      <c r="D599" s="57"/>
+      <c r="E599" s="58"/>
+      <c r="F599" s="59"/>
+      <c r="G599" s="59"/>
+      <c r="H599" s="60"/>
+      <c r="I599" s="57"/>
+      <c r="J599" s="61"/>
+      <c r="K599" s="1" t="str">
+        <f t="shared" si="75"/>
         <v>1900-01-00 :00</v>
       </c>
-      <c r="L576" s="1" t="str">
-        <f t="shared" si="51"/>
+      <c r="L599" s="1" t="str">
+        <f t="shared" si="76"/>
         <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
       </c>
     </row>
-    <row r="577" spans="1:12" ht="18.45">
-      <c r="A577" s="44"/>
-      <c r="B577" s="45" t="str">
-        <f t="shared" si="49"/>
+    <row r="600" spans="1:12" ht="18.45">
+      <c r="A600" s="44"/>
+      <c r="B600" s="45" t="str">
+        <f t="shared" si="74"/>
         <v>土</v>
       </c>
-      <c r="C577" s="57"/>
-      <c r="D577" s="57"/>
-      <c r="E577" s="58"/>
-      <c r="F577" s="59"/>
-      <c r="G577" s="59"/>
-      <c r="H577" s="60"/>
-      <c r="I577" s="57"/>
-      <c r="J577" s="61"/>
-      <c r="K577" s="1" t="str">
-        <f t="shared" si="50"/>
+      <c r="C600" s="57"/>
+      <c r="D600" s="57"/>
+      <c r="E600" s="58"/>
+      <c r="F600" s="59"/>
+      <c r="G600" s="59"/>
+      <c r="H600" s="60"/>
+      <c r="I600" s="57"/>
+      <c r="J600" s="61"/>
+      <c r="K600" s="1" t="str">
+        <f t="shared" si="75"/>
         <v>1900-01-00 :00</v>
       </c>
-      <c r="L577" s="1" t="str">
-        <f t="shared" si="51"/>
+      <c r="L600" s="1" t="str">
+        <f t="shared" si="76"/>
         <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
       </c>
     </row>
-    <row r="578" spans="1:12">
-      <c r="I578" s="21"/>
-      <c r="J578" s="21"/>
-    </row>
-    <row r="579" spans="1:12">
-      <c r="I579" s="21"/>
-      <c r="J579" s="21"/>
-    </row>
-    <row r="580" spans="1:12">
-      <c r="I580" s="21"/>
-      <c r="J580" s="21"/>
-    </row>
-    <row r="581" spans="1:12">
-      <c r="I581" s="21"/>
-      <c r="J581" s="21"/>
-    </row>
-    <row r="582" spans="1:12">
-      <c r="I582" s="21"/>
-      <c r="J582" s="21"/>
-    </row>
-    <row r="583" spans="1:12">
-      <c r="I583" s="21"/>
-      <c r="J583" s="21"/>
-    </row>
-    <row r="584" spans="1:12">
-      <c r="I584" s="21"/>
-      <c r="J584" s="21"/>
-    </row>
-    <row r="585" spans="1:12">
-      <c r="I585" s="21"/>
-      <c r="J585" s="21"/>
-    </row>
-    <row r="586" spans="1:12">
-      <c r="I586" s="21"/>
-      <c r="J586" s="21"/>
-    </row>
-    <row r="587" spans="1:12">
-      <c r="I587" s="21"/>
-      <c r="J587" s="21"/>
+    <row r="601" spans="1:12" ht="18.45">
+      <c r="A601" s="44"/>
+      <c r="B601" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C601" s="57"/>
+      <c r="D601" s="57"/>
+      <c r="E601" s="58"/>
+      <c r="F601" s="59"/>
+      <c r="G601" s="59"/>
+      <c r="H601" s="60"/>
+      <c r="I601" s="57"/>
+      <c r="J601" s="61"/>
+      <c r="K601" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L601" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="602" spans="1:12" ht="18.45">
+      <c r="A602" s="44"/>
+      <c r="B602" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C602" s="57"/>
+      <c r="D602" s="57"/>
+      <c r="E602" s="58"/>
+      <c r="F602" s="59"/>
+      <c r="G602" s="59"/>
+      <c r="H602" s="60"/>
+      <c r="I602" s="57"/>
+      <c r="J602" s="61"/>
+      <c r="K602" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L602" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="603" spans="1:12" ht="18.45">
+      <c r="A603" s="44"/>
+      <c r="B603" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C603" s="57"/>
+      <c r="D603" s="57"/>
+      <c r="E603" s="58"/>
+      <c r="F603" s="59"/>
+      <c r="G603" s="59"/>
+      <c r="H603" s="60"/>
+      <c r="I603" s="57"/>
+      <c r="J603" s="61"/>
+      <c r="K603" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L603" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="604" spans="1:12" ht="18.45">
+      <c r="A604" s="44"/>
+      <c r="B604" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C604" s="57"/>
+      <c r="D604" s="57"/>
+      <c r="E604" s="58"/>
+      <c r="F604" s="59"/>
+      <c r="G604" s="59"/>
+      <c r="H604" s="60"/>
+      <c r="I604" s="57"/>
+      <c r="J604" s="61"/>
+      <c r="K604" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L604" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="605" spans="1:12" ht="18.45">
+      <c r="A605" s="44"/>
+      <c r="B605" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C605" s="57"/>
+      <c r="D605" s="57"/>
+      <c r="E605" s="58"/>
+      <c r="F605" s="59"/>
+      <c r="G605" s="59"/>
+      <c r="H605" s="60"/>
+      <c r="I605" s="57"/>
+      <c r="J605" s="61"/>
+      <c r="K605" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L605" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="606" spans="1:12" ht="18.45">
+      <c r="A606" s="44"/>
+      <c r="B606" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C606" s="57"/>
+      <c r="D606" s="57"/>
+      <c r="E606" s="58"/>
+      <c r="F606" s="59"/>
+      <c r="G606" s="59"/>
+      <c r="H606" s="60"/>
+      <c r="I606" s="57"/>
+      <c r="J606" s="61"/>
+      <c r="K606" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L606" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="607" spans="1:12" ht="18.45">
+      <c r="A607" s="44"/>
+      <c r="B607" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C607" s="57"/>
+      <c r="D607" s="57"/>
+      <c r="E607" s="58"/>
+      <c r="F607" s="59"/>
+      <c r="G607" s="59"/>
+      <c r="H607" s="60"/>
+      <c r="I607" s="57"/>
+      <c r="J607" s="61"/>
+      <c r="K607" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L607" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="608" spans="1:12" ht="18.45">
+      <c r="A608" s="44"/>
+      <c r="B608" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C608" s="57"/>
+      <c r="D608" s="57"/>
+      <c r="E608" s="58"/>
+      <c r="F608" s="59"/>
+      <c r="G608" s="59"/>
+      <c r="H608" s="60"/>
+      <c r="I608" s="57"/>
+      <c r="J608" s="61"/>
+      <c r="K608" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L608" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="609" spans="1:12" ht="18.45">
+      <c r="A609" s="44"/>
+      <c r="B609" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C609" s="57"/>
+      <c r="D609" s="57"/>
+      <c r="E609" s="58"/>
+      <c r="F609" s="59"/>
+      <c r="G609" s="59"/>
+      <c r="H609" s="60"/>
+      <c r="I609" s="57"/>
+      <c r="J609" s="61"/>
+      <c r="K609" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L609" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="610" spans="1:12" ht="18.45">
+      <c r="A610" s="44"/>
+      <c r="B610" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C610" s="57"/>
+      <c r="D610" s="57"/>
+      <c r="E610" s="58"/>
+      <c r="F610" s="59"/>
+      <c r="G610" s="59"/>
+      <c r="H610" s="60"/>
+      <c r="I610" s="57"/>
+      <c r="J610" s="61"/>
+      <c r="K610" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L610" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="611" spans="1:12" ht="18.45">
+      <c r="A611" s="44"/>
+      <c r="B611" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C611" s="57"/>
+      <c r="D611" s="57"/>
+      <c r="E611" s="58"/>
+      <c r="F611" s="59"/>
+      <c r="G611" s="59"/>
+      <c r="H611" s="60"/>
+      <c r="I611" s="57"/>
+      <c r="J611" s="61"/>
+      <c r="K611" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L611" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="612" spans="1:12" ht="18.45">
+      <c r="A612" s="44"/>
+      <c r="B612" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C612" s="57"/>
+      <c r="D612" s="57"/>
+      <c r="E612" s="58"/>
+      <c r="F612" s="59"/>
+      <c r="G612" s="59"/>
+      <c r="H612" s="60"/>
+      <c r="I612" s="57"/>
+      <c r="J612" s="61"/>
+      <c r="K612" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L612" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="613" spans="1:12" ht="18.45">
+      <c r="A613" s="44"/>
+      <c r="B613" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C613" s="57"/>
+      <c r="D613" s="57"/>
+      <c r="E613" s="58"/>
+      <c r="F613" s="59"/>
+      <c r="G613" s="59"/>
+      <c r="H613" s="60"/>
+      <c r="I613" s="57"/>
+      <c r="J613" s="61"/>
+      <c r="K613" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L613" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="614" spans="1:12" ht="18.45">
+      <c r="A614" s="44"/>
+      <c r="B614" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C614" s="57"/>
+      <c r="D614" s="57"/>
+      <c r="E614" s="58"/>
+      <c r="F614" s="59"/>
+      <c r="G614" s="59"/>
+      <c r="H614" s="60"/>
+      <c r="I614" s="57"/>
+      <c r="J614" s="61"/>
+      <c r="K614" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L614" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="615" spans="1:12" ht="18.45">
+      <c r="A615" s="44"/>
+      <c r="B615" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C615" s="57"/>
+      <c r="D615" s="57"/>
+      <c r="E615" s="58"/>
+      <c r="F615" s="59"/>
+      <c r="G615" s="59"/>
+      <c r="H615" s="60"/>
+      <c r="I615" s="57"/>
+      <c r="J615" s="61"/>
+      <c r="K615" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L615" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="616" spans="1:12" ht="18.45">
+      <c r="A616" s="44"/>
+      <c r="B616" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C616" s="57"/>
+      <c r="D616" s="57"/>
+      <c r="E616" s="58"/>
+      <c r="F616" s="59"/>
+      <c r="G616" s="59"/>
+      <c r="H616" s="60"/>
+      <c r="I616" s="57"/>
+      <c r="J616" s="61"/>
+      <c r="K616" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L616" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="617" spans="1:12" ht="18.45">
+      <c r="A617" s="44"/>
+      <c r="B617" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C617" s="57"/>
+      <c r="D617" s="57"/>
+      <c r="E617" s="58"/>
+      <c r="F617" s="59"/>
+      <c r="G617" s="59"/>
+      <c r="H617" s="60"/>
+      <c r="I617" s="57"/>
+      <c r="J617" s="61"/>
+      <c r="K617" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L617" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="618" spans="1:12" ht="18.45">
+      <c r="A618" s="44"/>
+      <c r="B618" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C618" s="57"/>
+      <c r="D618" s="57"/>
+      <c r="E618" s="58"/>
+      <c r="F618" s="59"/>
+      <c r="G618" s="59"/>
+      <c r="H618" s="60"/>
+      <c r="I618" s="57"/>
+      <c r="J618" s="61"/>
+      <c r="K618" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L618" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="619" spans="1:12" ht="18.45">
+      <c r="A619" s="44"/>
+      <c r="B619" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C619" s="57"/>
+      <c r="D619" s="57"/>
+      <c r="E619" s="58"/>
+      <c r="F619" s="59"/>
+      <c r="G619" s="59"/>
+      <c r="H619" s="60"/>
+      <c r="I619" s="57"/>
+      <c r="J619" s="61"/>
+      <c r="K619" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L619" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="620" spans="1:12" ht="18.45">
+      <c r="A620" s="44"/>
+      <c r="B620" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C620" s="57"/>
+      <c r="D620" s="57"/>
+      <c r="E620" s="58"/>
+      <c r="F620" s="59"/>
+      <c r="G620" s="59"/>
+      <c r="H620" s="60"/>
+      <c r="I620" s="57"/>
+      <c r="J620" s="61"/>
+      <c r="K620" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L620" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="621" spans="1:12" ht="18.45">
+      <c r="A621" s="44"/>
+      <c r="B621" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C621" s="57"/>
+      <c r="D621" s="57"/>
+      <c r="E621" s="58"/>
+      <c r="F621" s="59"/>
+      <c r="G621" s="59"/>
+      <c r="H621" s="60"/>
+      <c r="I621" s="57"/>
+      <c r="J621" s="61"/>
+      <c r="K621" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L621" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="622" spans="1:12" ht="18.45">
+      <c r="A622" s="44"/>
+      <c r="B622" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C622" s="57"/>
+      <c r="D622" s="57"/>
+      <c r="E622" s="58"/>
+      <c r="F622" s="59"/>
+      <c r="G622" s="59"/>
+      <c r="H622" s="60"/>
+      <c r="I622" s="57"/>
+      <c r="J622" s="61"/>
+      <c r="K622" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L622" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="623" spans="1:12" ht="18.45">
+      <c r="A623" s="44"/>
+      <c r="B623" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C623" s="57"/>
+      <c r="D623" s="57"/>
+      <c r="E623" s="58"/>
+      <c r="F623" s="59"/>
+      <c r="G623" s="59"/>
+      <c r="H623" s="60"/>
+      <c r="I623" s="57"/>
+      <c r="J623" s="61"/>
+      <c r="K623" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L623" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="624" spans="1:12" ht="18.45">
+      <c r="A624" s="44"/>
+      <c r="B624" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C624" s="57"/>
+      <c r="D624" s="57"/>
+      <c r="E624" s="58"/>
+      <c r="F624" s="59"/>
+      <c r="G624" s="59"/>
+      <c r="H624" s="60"/>
+      <c r="I624" s="57"/>
+      <c r="J624" s="61"/>
+      <c r="K624" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L624" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="625" spans="1:12" ht="18.45">
+      <c r="A625" s="44"/>
+      <c r="B625" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C625" s="57"/>
+      <c r="D625" s="57"/>
+      <c r="E625" s="58"/>
+      <c r="F625" s="59"/>
+      <c r="G625" s="59"/>
+      <c r="H625" s="60"/>
+      <c r="I625" s="57"/>
+      <c r="J625" s="61"/>
+      <c r="K625" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L625" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="626" spans="1:12" ht="18.45">
+      <c r="A626" s="44"/>
+      <c r="B626" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C626" s="57"/>
+      <c r="D626" s="57"/>
+      <c r="E626" s="58"/>
+      <c r="F626" s="59"/>
+      <c r="G626" s="59"/>
+      <c r="H626" s="60"/>
+      <c r="I626" s="57"/>
+      <c r="J626" s="61"/>
+      <c r="K626" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L626" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="627" spans="1:12" ht="18.45">
+      <c r="A627" s="44"/>
+      <c r="B627" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C627" s="57"/>
+      <c r="D627" s="57"/>
+      <c r="E627" s="58"/>
+      <c r="F627" s="59"/>
+      <c r="G627" s="59"/>
+      <c r="H627" s="60"/>
+      <c r="I627" s="57"/>
+      <c r="J627" s="61"/>
+      <c r="K627" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L627" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="628" spans="1:12" ht="18.45">
+      <c r="A628" s="44"/>
+      <c r="B628" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C628" s="57"/>
+      <c r="D628" s="57"/>
+      <c r="E628" s="58"/>
+      <c r="F628" s="59"/>
+      <c r="G628" s="59"/>
+      <c r="H628" s="60"/>
+      <c r="I628" s="57"/>
+      <c r="J628" s="61"/>
+      <c r="K628" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L628" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="629" spans="1:12" ht="18.45">
+      <c r="A629" s="44"/>
+      <c r="B629" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C629" s="57"/>
+      <c r="D629" s="57"/>
+      <c r="E629" s="58"/>
+      <c r="F629" s="59"/>
+      <c r="G629" s="59"/>
+      <c r="H629" s="60"/>
+      <c r="I629" s="57"/>
+      <c r="J629" s="61"/>
+      <c r="K629" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L629" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="630" spans="1:12" ht="18.45">
+      <c r="A630" s="44"/>
+      <c r="B630" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C630" s="57"/>
+      <c r="D630" s="57"/>
+      <c r="E630" s="58"/>
+      <c r="F630" s="59"/>
+      <c r="G630" s="59"/>
+      <c r="H630" s="60"/>
+      <c r="I630" s="57"/>
+      <c r="J630" s="61"/>
+      <c r="K630" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L630" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="631" spans="1:12" ht="18.45">
+      <c r="A631" s="44"/>
+      <c r="B631" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C631" s="57"/>
+      <c r="D631" s="57"/>
+      <c r="E631" s="58"/>
+      <c r="F631" s="59"/>
+      <c r="G631" s="59"/>
+      <c r="H631" s="60"/>
+      <c r="I631" s="57"/>
+      <c r="J631" s="61"/>
+      <c r="K631" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L631" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="632" spans="1:12" ht="18.45">
+      <c r="A632" s="44"/>
+      <c r="B632" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C632" s="57"/>
+      <c r="D632" s="57"/>
+      <c r="E632" s="58"/>
+      <c r="F632" s="59"/>
+      <c r="G632" s="59"/>
+      <c r="H632" s="60"/>
+      <c r="I632" s="57"/>
+      <c r="J632" s="61"/>
+      <c r="K632" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L632" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="633" spans="1:12" ht="18.45">
+      <c r="A633" s="44"/>
+      <c r="B633" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C633" s="57"/>
+      <c r="D633" s="57"/>
+      <c r="E633" s="58"/>
+      <c r="F633" s="59"/>
+      <c r="G633" s="59"/>
+      <c r="H633" s="60"/>
+      <c r="I633" s="57"/>
+      <c r="J633" s="61"/>
+      <c r="K633" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L633" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="634" spans="1:12" ht="18.45">
+      <c r="A634" s="44"/>
+      <c r="B634" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C634" s="57"/>
+      <c r="D634" s="57"/>
+      <c r="E634" s="58"/>
+      <c r="F634" s="59"/>
+      <c r="G634" s="59"/>
+      <c r="H634" s="60"/>
+      <c r="I634" s="57"/>
+      <c r="J634" s="61"/>
+      <c r="K634" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L634" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="635" spans="1:12" ht="18.45">
+      <c r="A635" s="44"/>
+      <c r="B635" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C635" s="57"/>
+      <c r="D635" s="57"/>
+      <c r="E635" s="58"/>
+      <c r="F635" s="59"/>
+      <c r="G635" s="59"/>
+      <c r="H635" s="60"/>
+      <c r="I635" s="57"/>
+      <c r="J635" s="61"/>
+      <c r="K635" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L635" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="636" spans="1:12" ht="18.45">
+      <c r="A636" s="44"/>
+      <c r="B636" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C636" s="57"/>
+      <c r="D636" s="57"/>
+      <c r="E636" s="58"/>
+      <c r="F636" s="59"/>
+      <c r="G636" s="59"/>
+      <c r="H636" s="60"/>
+      <c r="I636" s="57"/>
+      <c r="J636" s="61"/>
+      <c r="K636" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L636" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="637" spans="1:12" ht="18.45">
+      <c r="A637" s="44"/>
+      <c r="B637" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C637" s="57"/>
+      <c r="D637" s="57"/>
+      <c r="E637" s="58"/>
+      <c r="F637" s="59"/>
+      <c r="G637" s="59"/>
+      <c r="H637" s="60"/>
+      <c r="I637" s="57"/>
+      <c r="J637" s="61"/>
+      <c r="K637" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L637" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="638" spans="1:12" ht="18.45">
+      <c r="A638" s="44"/>
+      <c r="B638" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C638" s="57"/>
+      <c r="D638" s="57"/>
+      <c r="E638" s="58"/>
+      <c r="F638" s="59"/>
+      <c r="G638" s="59"/>
+      <c r="H638" s="60"/>
+      <c r="I638" s="57"/>
+      <c r="J638" s="61"/>
+      <c r="K638" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L638" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="639" spans="1:12" ht="18.45">
+      <c r="A639" s="44"/>
+      <c r="B639" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C639" s="57"/>
+      <c r="D639" s="57"/>
+      <c r="E639" s="58"/>
+      <c r="F639" s="59"/>
+      <c r="G639" s="59"/>
+      <c r="H639" s="60"/>
+      <c r="I639" s="57"/>
+      <c r="J639" s="61"/>
+      <c r="K639" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L639" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="640" spans="1:12" ht="18.45">
+      <c r="A640" s="44"/>
+      <c r="B640" s="45" t="str">
+        <f t="shared" si="74"/>
+        <v>土</v>
+      </c>
+      <c r="C640" s="57"/>
+      <c r="D640" s="57"/>
+      <c r="E640" s="58"/>
+      <c r="F640" s="59"/>
+      <c r="G640" s="59"/>
+      <c r="H640" s="60"/>
+      <c r="I640" s="57"/>
+      <c r="J640" s="61"/>
+      <c r="K640" s="1" t="str">
+        <f t="shared" si="75"/>
+        <v>1900-01-00 :00</v>
+      </c>
+      <c r="L640" s="1" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve"> (NULL, '1900-01-00 :00', NULL, '', NULL, '', NULL, '', NULL, NOW(), NOW()),</v>
+      </c>
+    </row>
+    <row r="641" spans="9:10">
+      <c r="I641" s="21"/>
+      <c r="J641" s="21"/>
+    </row>
+    <row r="642" spans="9:10">
+      <c r="I642" s="21"/>
+      <c r="J642" s="21"/>
+    </row>
+    <row r="643" spans="9:10">
+      <c r="I643" s="21"/>
+      <c r="J643" s="21"/>
+    </row>
+    <row r="644" spans="9:10">
+      <c r="I644" s="21"/>
+      <c r="J644" s="21"/>
+    </row>
+    <row r="645" spans="9:10">
+      <c r="I645" s="21"/>
+      <c r="J645" s="21"/>
+    </row>
+    <row r="646" spans="9:10">
+      <c r="I646" s="21"/>
+      <c r="J646" s="21"/>
+    </row>
+    <row r="647" spans="9:10">
+      <c r="I647" s="21"/>
+      <c r="J647" s="21"/>
+    </row>
+    <row r="648" spans="9:10">
+      <c r="I648" s="21"/>
+      <c r="J648" s="21"/>
+    </row>
+    <row r="649" spans="9:10">
+      <c r="I649" s="21"/>
+      <c r="J649" s="21"/>
+    </row>
+    <row r="650" spans="9:10">
+      <c r="I650" s="21"/>
+      <c r="J650" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:K368" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -23735,7 +26672,7 @@
     <hyperlink ref="J467" r:id="rId165" xr:uid="{C1FD3A2E-38FA-4B37-97AC-AA257046CB01}"/>
     <hyperlink ref="J473" r:id="rId166" xr:uid="{5615E09B-DDC0-4A31-863C-9897F36C639B}"/>
     <hyperlink ref="J493" r:id="rId167" xr:uid="{E4BC5E63-AC7B-4337-8188-AF8BFBDE1F8D}"/>
-    <hyperlink ref="J502" r:id="rId168" xr:uid="{A2FE4E3B-90C9-4B92-90A1-FE959B9FCE7D}"/>
+    <hyperlink ref="J533" r:id="rId168" xr:uid="{A2FE4E3B-90C9-4B92-90A1-FE959B9FCE7D}"/>
     <hyperlink ref="J466" r:id="rId169" xr:uid="{23A4617D-0CB4-484B-9931-4D5E80D5B704}"/>
     <hyperlink ref="J457" r:id="rId170" xr:uid="{21E579D3-BF50-452E-B2CF-9C56CFEEDAA8}"/>
     <hyperlink ref="J469" r:id="rId171" xr:uid="{A5FB896E-C35D-4C0B-8ED7-D37201F7CE55}"/>
@@ -23754,26 +26691,26 @@
     <hyperlink ref="J478" r:id="rId184" xr:uid="{665FC563-9FD7-422C-A19E-4D62C876A957}"/>
     <hyperlink ref="J488" r:id="rId185" xr:uid="{D2AE0D35-08AF-462B-8415-FEA9E8E9B701}"/>
     <hyperlink ref="J482" r:id="rId186" xr:uid="{59C2ABEC-22D7-44C7-B8C2-FCA5DB419D2A}"/>
-    <hyperlink ref="J501" r:id="rId187" xr:uid="{93D2779E-5DBA-44C0-BDF2-E4359D7D8D6F}"/>
-    <hyperlink ref="J505" r:id="rId188" xr:uid="{76EFB001-AF41-4915-B3EA-F1F429043636}"/>
+    <hyperlink ref="J531" r:id="rId187" xr:uid="{93D2779E-5DBA-44C0-BDF2-E4359D7D8D6F}"/>
+    <hyperlink ref="J568" r:id="rId188" xr:uid="{76EFB001-AF41-4915-B3EA-F1F429043636}"/>
     <hyperlink ref="J461" r:id="rId189" xr:uid="{2A28CBA3-90B1-4091-B072-E18C71606105}"/>
     <hyperlink ref="J487" r:id="rId190" xr:uid="{D31C5BEF-5617-40AB-A000-0E18BE8E8AED}"/>
     <hyperlink ref="J479" r:id="rId191" xr:uid="{3EED5E26-3341-4027-8560-696994EC743E}"/>
-    <hyperlink ref="J497" r:id="rId192" xr:uid="{6D49912A-9881-4A9F-980E-79CE253F9313}"/>
+    <hyperlink ref="J503" r:id="rId192" xr:uid="{6D49912A-9881-4A9F-980E-79CE253F9313}"/>
     <hyperlink ref="J459" r:id="rId193" xr:uid="{E981E541-FF26-4B20-B212-4AE2FF064B8E}"/>
     <hyperlink ref="J460" r:id="rId194" xr:uid="{0DF011A1-A5EC-4D87-AB60-21F9F61048FD}"/>
     <hyperlink ref="J471" r:id="rId195" xr:uid="{128D98CC-82A0-40E0-A678-95758302878D}"/>
     <hyperlink ref="J475" r:id="rId196" xr:uid="{3754054F-6B0F-475A-990A-008470B7ACE7}"/>
     <hyperlink ref="J491" r:id="rId197" xr:uid="{DE1C2CC2-36B6-4C1D-8B82-58A5243634DE}"/>
     <hyperlink ref="J492" r:id="rId198" xr:uid="{BCCE8FD8-B907-49D9-B805-CBC28F663A38}"/>
-    <hyperlink ref="J499" r:id="rId199" xr:uid="{C377A97C-A591-4F57-BB66-CF9AC0F39621}"/>
+    <hyperlink ref="J506" r:id="rId199" xr:uid="{C377A97C-A591-4F57-BB66-CF9AC0F39621}"/>
     <hyperlink ref="J477" r:id="rId200" xr:uid="{FE635402-F200-4D53-9041-37C29E34F5A1}"/>
     <hyperlink ref="J470" r:id="rId201" xr:uid="{28D709C8-74F8-41C7-A506-043F95903716}"/>
     <hyperlink ref="J484" r:id="rId202" xr:uid="{1F331497-0D77-4123-B337-6E4BACC09796}"/>
-    <hyperlink ref="J498" r:id="rId203" xr:uid="{A6C98AE4-40BF-4ED3-BBBB-21F973CAE664}"/>
+    <hyperlink ref="J505" r:id="rId203" xr:uid="{A6C98AE4-40BF-4ED3-BBBB-21F973CAE664}"/>
     <hyperlink ref="J490" r:id="rId204" xr:uid="{6FE51F84-7606-4918-8603-DA0FEB34A0E3}"/>
     <hyperlink ref="J465" r:id="rId205" xr:uid="{9A3E8291-528C-4AE9-81EE-558E4456BE8E}"/>
-    <hyperlink ref="J504" r:id="rId206" xr:uid="{E4873FB5-92B0-4FF4-9EFB-BCF6E871F34B}"/>
+    <hyperlink ref="J558" r:id="rId206" xr:uid="{E4873FB5-92B0-4FF4-9EFB-BCF6E871F34B}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="40" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId207"/>
